--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'详细表'!$A$1:$F$120</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待补-部分'!$A$1:$F$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待补-部分'!$A$1:$F$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -116,13 +116,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -562,33 +562,33 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>未实现</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>近似（倍率推断）</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>近似（倍率推断）</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>仅属性（触发未实现）</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>仅属性（触发未实现）</t>
+          <t>未实现</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -624,7 +624,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>独立脚本（攻击扣蓝10%；蓝耗+25%未做）</t>
+          <t>独立脚本（召唤回主人28%生命）</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -632,9 +632,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>近似（封心+护盾已接）</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>独立脚本（攻击扣蓝10%；蓝耗+25%未做）</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -642,9 +642,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>独立脚本（攻击扣蓝15%）</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>近似（封心+护盾已接）</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -652,9 +652,9 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>近似（20%暴击吸血）</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>独立脚本（攻击扣蓝15%）</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -662,9 +662,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>独立脚本（真实伤害）</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>近似（20%暴击吸血）</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -674,7 +674,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>独立脚本（物理受击护盾）</t>
+          <t>独立脚本（真实伤害）</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -682,9 +682,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>近似（群增伤20%）</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>独立脚本（物理受击护盾）</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -692,9 +692,9 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>独立脚本（出场盾+受击魔法盾）</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>近似（群增伤20%）</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -704,7 +704,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>精确（当前生命25%脚本）</t>
+          <t>独立脚本（出场盾+受击魔法盾）</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -712,9 +712,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>部分（随机形态未做）</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>精确（当前生命25%脚本）</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -724,7 +724,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>部分（叠层已做，伤害分担未做）</t>
+          <t>部分（随机形态未做）</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -732,9 +732,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>独立脚本（减伤/反伤/沉默）</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>部分（叠层已做，伤害分担未做）</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -742,9 +742,9 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>近似（50%暴击吸血）</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>独立脚本（减伤/反伤/沉默）</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -752,9 +752,9 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>近似（10%法术吸血）</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>独立脚本（死亡回全队40%生命）</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -764,7 +764,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>近似（护盾+10%免疫）</t>
+          <t>近似（50%暴击吸血）</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -772,9 +772,9 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>未实现（伤害分担）</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>近似（10%法术吸血）</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -784,7 +784,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>独立脚本（25%法术吸血+受击减伤）</t>
+          <t>独立脚本（随机双/三倍+速度增伤）</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -792,9 +792,9 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>独立脚本（击杀回血+燃火增伤）</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>近似（护盾+10%免疫）</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -802,9 +802,9 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>部分（属性/法穿已做，怒气未做）</t>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>未实现（伤害分担）</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -812,9 +812,9 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>部分（附加治疗/护盾未做）</t>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>独立脚本（25%法术吸血+受击减伤）</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -822,59 +822,89 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>部分（溅射近似）</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>独立脚本（击杀回血+燃火增伤）</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>部分（属性/法穿已做，怒气未做）</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>部分（附加治疗/护盾未做）</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>部分（溅射近似）</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>独立脚本：700001-700005 等专用脚本</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>精确：属性/公式按说明落表</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>近似：属性/目标/消耗准确，伤害倍率或 buff 参数推断</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>部分：部分机制已做，剩余机制未做</t>
+          <t>独立脚本：700001-700005 等专用脚本</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>未实现：目前没有生效记录</t>
+          <t>精确：属性/公式按说明落表</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
+        <is>
+          <t>近似：属性/目标/消耗准确，伤害倍率或 buff 参数推断</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>部分：部分机制已做，剩余机制未做</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>未实现：目前没有生效记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>伤害倍率无法从客户端取得，均为推断值</t>
         </is>
@@ -945,17 +975,17 @@
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>召唤回主人血；目标1；倍率[1000]</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>独立脚本（召唤回主人28%生命）</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
@@ -983,7 +1013,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>未实现</t>
         </is>
@@ -1013,7 +1043,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>未实现</t>
         </is>
@@ -1043,7 +1073,7 @@
           <t>脚本32000(610, 550, 1000)；目标1；倍率[1000]；CD1</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1073,7 +1103,7 @@
           <t>脚本32001(400, 350, 0, 75)；目标1；倍率[1000]；CD4</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1103,7 +1133,7 @@
           <t>攻击扣蓝；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>独立脚本（攻击扣蓝10%；蓝耗+25%未做）</t>
         </is>
@@ -1133,7 +1163,7 @@
           <t>神佑(140, 180, 220, 280, 1000, 0)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1163,7 +1193,7 @@
           <t>逃生(490, 0, 150)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1193,7 +1223,7 @@
           <t>反弹(350, 650)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1223,7 +1253,7 @@
           <t>还击(580, [60011, 60012, 60013)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1253,7 +1283,7 @@
           <t>物理攻击(500, 300, 100)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1283,7 +1313,7 @@
           <t>审判(350)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1313,7 +1343,7 @@
           <t>驱鬼(1000, 80)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1343,7 +1373,7 @@
           <t>脚本31000(380)；目标1；倍率[1000]；buff:物攻祝福(2回合)</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1373,7 +1403,7 @@
           <t>生命=等级×55.0+380</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
@@ -1403,7 +1433,7 @@
           <t>逆击(330)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1433,7 +1463,7 @@
           <t>攻速%+15.0%</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
@@ -1463,7 +1493,7 @@
           <t>物防=等级×12.0+88</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
@@ -1493,7 +1523,7 @@
           <t>魔防=等级×12.0+88</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
@@ -1523,7 +1553,7 @@
           <t>命中+140；强击(150, 1700, 650)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1553,7 +1583,7 @@
           <t>物穿(400)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1583,7 +1613,7 @@
           <t>生命%+5.0%，魔攻%+3.0%；法术连击；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1613,7 +1643,7 @@
           <t>闪避+100，攻速%+35.0%</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
@@ -1643,7 +1673,7 @@
           <t>攻速%+20.0%；眩晕(800, 800, 800, 800)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1673,7 +1703,7 @@
           <t>生命+30000，伤害加成+15.0%</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>仅属性（触发未实现）</t>
         </is>
@@ -1703,7 +1733,7 @@
           <t>魔攻%+20.0%；魔法攻击(0)；目标4；倍率[1800]</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
@@ -1733,7 +1763,7 @@
           <t>物穿(0)；目标1；倍率[700, 700]；2段</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
@@ -1763,7 +1793,7 @@
           <t>吸血(1000, 150)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1793,7 +1823,7 @@
           <t>禁魂(1000, 1000)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -1823,7 +1853,7 @@
           <t>暴伤+40.0%</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
@@ -1853,7 +1883,7 @@
           <t>暴击+25.0%，物伤加成+20.0%，攻速%+10.0%，魔防%+20.0%</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>仅属性（触发未实现）</t>
         </is>
@@ -1883,7 +1913,7 @@
           <t>治疗(80, 200)；目标3；倍率[1000]；buff:持续回血(每回合5.0%，3回合)</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>近似（治疗/护盾参数）</t>
         </is>
@@ -1913,7 +1943,7 @@
           <t>魔法攻击(0)；目标3；倍率[1600]；MP99；buff:生命护盾(生命上限200.0%，2回合)、封心(封心50.0%，2回合)</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>近似（封心+护盾已接）</t>
         </is>
@@ -1943,7 +1973,7 @@
           <t>生命%+30.0%，攻速%+15.0%，物防%+25.0%，魔防%+25.0%</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
@@ -1973,7 +2003,7 @@
           <t>攻速%+12.0%，魔攻%+10.0%，物防%+12.0%</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>仅属性（触发未实现）</t>
         </is>
@@ -2003,7 +2033,7 @@
           <t>攻击扣蓝；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>独立脚本（攻击扣蓝15%）</t>
         </is>
@@ -2033,7 +2063,7 @@
           <t>暴伤+20.0%；法术连击；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -2063,7 +2093,7 @@
           <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤99(每层10.0%，999回合)</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -2093,7 +2123,7 @@
           <t>暴击+15.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>仅属性（触发未实现）</t>
         </is>
@@ -2123,7 +2153,7 @@
           <t>物理攻击(暴击吸血)(200)；目标4；倍率[1800]</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>近似（20%暴击吸血）</t>
         </is>
@@ -2153,7 +2183,7 @@
           <t>攻速%+12.0%，物防%+12.0%，魔防%+15.0%</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
@@ -2183,7 +2213,7 @@
           <t>连击(500, 0, 1800, 1800)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -2213,7 +2243,7 @@
           <t>生命%+35.0%，攻速%+18.0%，物防%+30.0%，魔防%+30.0%；被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，2回合)</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -2243,7 +2273,7 @@
           <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，2回合)、反伤(20.0%反伤，999回合)</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -2273,7 +2303,7 @@
           <t>暴击+20.0%，攻速%+15.0%，物攻%+15.0%，魔防%+20.0%</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>仅属性（触发未实现）</t>
         </is>
@@ -2303,7 +2333,7 @@
           <t>真实伤害(500)；目标4；倍率[1800]</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr">
         <is>
           <t>独立脚本（真实伤害）</t>
         </is>
@@ -2333,7 +2363,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="E48" s="10" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>未实现</t>
         </is>
@@ -2363,7 +2393,7 @@
           <t>攻速%+12.0%，物攻%+15.0%，物防%+12.0%</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="10" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
@@ -2393,7 +2423,7 @@
           <t>治疗(120, 200)；目标4；倍率[1000]；buff:持续回血(每回合8.0%，3回合)</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>近似（治疗/护盾参数）</t>
         </is>
@@ -2423,7 +2453,7 @@
           <t>回蓝(300, 0)；目标5；倍率[1000]；MP3</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>近似（治疗/护盾参数）</t>
         </is>
@@ -2453,7 +2483,7 @@
           <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，2回合)、反伤(20.0%反伤，999回合)</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -2483,7 +2513,7 @@
           <t>生命%+30.0%，攻速%+20.0%，物防%+25.0%，魔防%+25.0%；物理受击护盾(200, 300, 2)；目标1；倍率[1000]；CD1</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="10" t="inlineStr">
         <is>
           <t>独立脚本（物理受击护盾）</t>
         </is>
@@ -2513,7 +2543,7 @@
           <t>纯 buff；目标13；倍率[1000]；MP4；CD2；buff:减伤(50.0%减伤，3回合)</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
+      <c r="E54" s="12" t="inlineStr">
         <is>
           <t>近似（治疗/护盾参数）</t>
         </is>
@@ -2543,7 +2573,7 @@
           <t>纯 buff；目标1；倍率[1000]；buff:反伤(35.0%反伤，3回合)</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr">
+      <c r="E55" s="12" t="inlineStr">
         <is>
           <t>近似（治疗/护盾参数）</t>
         </is>
@@ -2573,7 +2603,7 @@
           <t>纯 buff；目标13；倍率[1000]；MP4；CD2；buff:增伤(20.0%增伤，3回合)</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr">
+      <c r="E56" s="12" t="inlineStr">
         <is>
           <t>近似（群增伤20%）</t>
         </is>
@@ -2603,7 +2633,7 @@
           <t>生命%+30.0%，攻速%+20.0%，物防%+25.0%，魔防%+25.0%；出场盾+受击魔法盾；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="E57" s="10" t="inlineStr">
         <is>
           <t>独立脚本（出场盾+受击魔法盾）</t>
         </is>
@@ -2633,7 +2663,7 @@
           <t>物理攻击(暴击吸血)(0)；目标7；倍率[1200]；MP1；CD1</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr">
+      <c r="E58" s="12" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
@@ -2663,7 +2693,7 @@
           <t>脚本20023(1, 250, 0)；目标1；倍率[0]</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E59" s="10" t="inlineStr">
         <is>
           <t>精确（当前生命25%脚本）</t>
         </is>
@@ -2693,7 +2723,7 @@
           <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤3(每层15.0%，999回合)</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr">
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -2723,7 +2753,7 @@
           <t>攻速%+15.0%，物攻%+15.0%，物防%+20.0%，魔防%+20.0%</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr">
+      <c r="E61" s="11" t="inlineStr">
         <is>
           <t>仅属性（触发未实现）</t>
         </is>
@@ -2783,7 +2813,7 @@
           <t>暴击+20.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E63" s="11" t="inlineStr">
         <is>
           <t>仅属性（触发未实现）</t>
         </is>
@@ -2843,7 +2873,7 @@
           <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，2回合)</t>
         </is>
       </c>
-      <c r="E65" s="11" t="inlineStr">
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -2873,7 +2903,7 @@
           <t>被动触发；目标1；倍率[1000]；CD99；buff:复活(100.0%生命复活，999回合)</t>
         </is>
       </c>
-      <c r="E66" s="11" t="inlineStr">
+      <c r="E66" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -2903,7 +2933,7 @@
           <t>减伤/反伤/沉默；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E67" s="12" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr">
         <is>
           <t>独立脚本（减伤/反伤/沉默）</t>
         </is>
@@ -2925,17 +2955,17 @@
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>死亡回全队血；目标1；倍率[1000]</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>独立脚本（死亡回全队40%生命）</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
@@ -2963,7 +2993,7 @@
           <t>闪避+200，生命%+30.0%，物防%+25.0%，魔防%+25.0%；被动触发；目标1；倍率[1000]；CD99；buff:减伤(70.0%减伤，2回合)</t>
         </is>
       </c>
-      <c r="E69" s="11" t="inlineStr">
+      <c r="E69" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -2993,7 +3023,7 @@
           <t>被动触发；目标1；倍率[1000]；CD99；buff:复活(80.0%生命复活，999回合)</t>
         </is>
       </c>
-      <c r="E70" s="11" t="inlineStr">
+      <c r="E70" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -3023,7 +3053,7 @@
           <t>物理攻击(暴击吸血)(0)；目标3；倍率[466, 466, 468]；3段</t>
         </is>
       </c>
-      <c r="E71" s="11" t="inlineStr">
+      <c r="E71" s="12" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
@@ -3053,7 +3083,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="E72" s="10" t="inlineStr">
+      <c r="E72" s="11" t="inlineStr">
         <is>
           <t>未实现</t>
         </is>
@@ -3083,7 +3113,7 @@
           <t>暴击+10.0%，攻速%+15.0%，物攻%+15.0%，魔防%+25.0%</t>
         </is>
       </c>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="E73" s="10" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
@@ -3113,7 +3143,7 @@
           <t>被动触发；目标1；倍率[1000]；CD99；buff:隐身(2回合)</t>
         </is>
       </c>
-      <c r="E74" s="11" t="inlineStr">
+      <c r="E74" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -3143,7 +3173,7 @@
           <t>魔法暴击+10.0%，攻速%+10.0%，魔攻%+15.0%，物防%+30.0%；被动触发；目标1；倍率[1000]；CD1；buff:减伤(20.0%减伤，2回合)</t>
         </is>
       </c>
-      <c r="E75" s="11" t="inlineStr">
+      <c r="E75" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -3173,7 +3203,7 @@
           <t>魔法攻击(0)；目标3；倍率[466, 466, 468]；3段</t>
         </is>
       </c>
-      <c r="E76" s="11" t="inlineStr">
+      <c r="E76" s="12" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
@@ -3203,7 +3233,7 @@
           <t>物理攻击(暴击吸血)(500)；目标4；倍率[700, 700]；2段</t>
         </is>
       </c>
-      <c r="E77" s="11" t="inlineStr">
+      <c r="E77" s="12" t="inlineStr">
         <is>
           <t>近似（50%暴击吸血）</t>
         </is>
@@ -3233,7 +3263,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="E78" s="10" t="inlineStr">
+      <c r="E78" s="11" t="inlineStr">
         <is>
           <t>未实现</t>
         </is>
@@ -3263,7 +3293,7 @@
           <t>连击(600, 0, 1350, 1350)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E79" s="11" t="inlineStr">
+      <c r="E79" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -3323,7 +3353,7 @@
           <t>魔法攻击(0)；目标4；倍率[700, 700]；2段；buff:法术吸血(10.0%吸血，1回合)</t>
         </is>
       </c>
-      <c r="E81" s="11" t="inlineStr">
+      <c r="E81" s="12" t="inlineStr">
         <is>
           <t>近似（10%法术吸血）</t>
         </is>
@@ -3353,7 +3383,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="E82" s="10" t="inlineStr">
+      <c r="E82" s="11" t="inlineStr">
         <is>
           <t>未实现</t>
         </is>
@@ -3383,7 +3413,7 @@
           <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限100.0%，1回合)</t>
         </is>
       </c>
-      <c r="E83" s="11" t="inlineStr">
+      <c r="E83" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -3413,7 +3443,7 @@
           <t>魔法暴击+15.0%，攻速%+12.0%，魔攻%+15.0%，物防%+25.0%；被动触发；目标1；倍率[1000]；CD1；buff:伤害免疫(50.0%免疫，1回合)</t>
         </is>
       </c>
-      <c r="E84" s="11" t="inlineStr">
+      <c r="E84" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -3443,7 +3473,7 @@
           <t>物理攻击(暴击吸血)(0)；目标4；倍率[466, 466, 468]；3段</t>
         </is>
       </c>
-      <c r="E85" s="11" t="inlineStr">
+      <c r="E85" s="12" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
@@ -3473,7 +3503,7 @@
           <t>连击(700, 0, 1200, 1200)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E86" s="11" t="inlineStr">
+      <c r="E86" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -3495,17 +3525,17 @@
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>随机双倍/三倍+速度增伤；目标1；倍率[1000]</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>独立脚本（随机双/三倍+速度增伤）</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr">
@@ -3533,7 +3563,7 @@
           <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限100.0%，1回合)、伤害免疫(10.0%免疫，999回合)</t>
         </is>
       </c>
-      <c r="E88" s="11" t="inlineStr">
+      <c r="E88" s="12" t="inlineStr">
         <is>
           <t>近似（护盾+10%免疫）</t>
         </is>
@@ -3593,7 +3623,7 @@
           <t>魔法攻击(0)；目标4；倍率[466, 466, 468]；3段</t>
         </is>
       </c>
-      <c r="E90" s="11" t="inlineStr">
+      <c r="E90" s="12" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
@@ -3623,7 +3653,7 @@
           <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤99(每层10.0%，999回合)</t>
         </is>
       </c>
-      <c r="E91" s="11" t="inlineStr">
+      <c r="E91" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -3653,7 +3683,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="E92" s="10" t="inlineStr">
+      <c r="E92" s="11" t="inlineStr">
         <is>
           <t>未实现（伤害分担）</t>
         </is>
@@ -3683,7 +3713,7 @@
           <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，1回合)</t>
         </is>
       </c>
-      <c r="E93" s="11" t="inlineStr">
+      <c r="E93" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -3713,7 +3743,7 @@
           <t>魔法暴击+20.0%，攻速%+18.0%，魔攻%+15.0%，物防%+25.0%</t>
         </is>
       </c>
-      <c r="E94" s="10" t="inlineStr">
+      <c r="E94" s="11" t="inlineStr">
         <is>
           <t>仅属性（触发未实现）</t>
         </is>
@@ -3743,7 +3773,7 @@
           <t>物理攻击(暴击吸血)(0)；目标3；倍率[700, 700]；2段</t>
         </is>
       </c>
-      <c r="E95" s="11" t="inlineStr">
+      <c r="E95" s="12" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
@@ -3773,7 +3803,7 @@
           <t>物攻%+5.0%，魔攻%+3.0%；连击(1000, 0, 1000, 1000)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E96" s="11" t="inlineStr">
+      <c r="E96" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -3803,7 +3833,7 @@
           <t>暴击+5.0%，攻速%+10.0%，物攻%+10.0%；物穿(100)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E97" s="11" t="inlineStr">
+      <c r="E97" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -3863,7 +3893,7 @@
           <t>物穿(280)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E99" s="11" t="inlineStr">
+      <c r="E99" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -3893,7 +3923,7 @@
           <t>禁魂(200, 200)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E100" s="11" t="inlineStr">
+      <c r="E100" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -3923,7 +3953,7 @@
           <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，1回合)</t>
         </is>
       </c>
-      <c r="E101" s="11" t="inlineStr">
+      <c r="E101" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -3953,7 +3983,7 @@
           <t>暴击+20.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%；物穿(350)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E102" s="11" t="inlineStr">
+      <c r="E102" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -3983,7 +4013,7 @@
           <t>魔法攻击(0)；目标6；倍率[466, 466, 468]；3段</t>
         </is>
       </c>
-      <c r="E103" s="11" t="inlineStr">
+      <c r="E103" s="12" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
@@ -4013,7 +4043,7 @@
           <t>法术吸血+受击减伤；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E104" s="12" t="inlineStr">
+      <c r="E104" s="10" t="inlineStr">
         <is>
           <t>独立脚本（25%法术吸血+受击减伤）</t>
         </is>
@@ -4043,7 +4073,7 @@
           <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤99(每层15.0%，999回合)</t>
         </is>
       </c>
-      <c r="E105" s="11" t="inlineStr">
+      <c r="E105" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -4073,7 +4103,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="E106" s="10" t="inlineStr">
+      <c r="E106" s="11" t="inlineStr">
         <is>
           <t>未实现</t>
         </is>
@@ -4103,7 +4133,7 @@
           <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；法穿(300)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E107" s="11" t="inlineStr">
+      <c r="E107" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -4163,7 +4193,7 @@
           <t>法穿(300)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E109" s="11" t="inlineStr">
+      <c r="E109" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -4193,7 +4223,7 @@
           <t>击杀回血+燃火；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E110" s="12" t="inlineStr">
+      <c r="E110" s="10" t="inlineStr">
         <is>
           <t>独立脚本（击杀回血+燃火增伤）</t>
         </is>
@@ -4223,7 +4253,7 @@
           <t>被动触发；目标1；倍率[1000]；CD99；buff:次数护盾(挡6次，1回合)</t>
         </is>
       </c>
-      <c r="E111" s="11" t="inlineStr">
+      <c r="E111" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -4313,7 +4343,7 @@
           <t>被动触发；目标1；倍率[1000]；CD99；buff:复活(150.0%生命复活，999回合)</t>
         </is>
       </c>
-      <c r="E114" s="11" t="inlineStr">
+      <c r="E114" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -4343,7 +4373,7 @@
           <t>连击(300, 0, 700, 700)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E115" s="11" t="inlineStr">
+      <c r="E115" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -4373,7 +4403,7 @@
           <t>被动触发；目标1；倍率[1000]；CD99；buff:次数护盾(挡6次，1回合)</t>
         </is>
       </c>
-      <c r="E116" s="11" t="inlineStr">
+      <c r="E116" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -4403,7 +4433,7 @@
           <t>暴击+20.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%；物穿(350)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E117" s="11" t="inlineStr">
+      <c r="E117" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -4463,7 +4493,7 @@
           <t>连击(400, 0, 1800, 1800)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E119" s="11" t="inlineStr">
+      <c r="E119" s="12" t="inlineStr">
         <is>
           <t>近似（触发脚本）</t>
         </is>
@@ -4493,7 +4523,7 @@
           <t>生命=等级×80.0+1000</t>
         </is>
       </c>
-      <c r="E120" s="12" t="inlineStr">
+      <c r="E120" s="10" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
@@ -4516,7 +4546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4561,11 +4591,11 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="n">
-        <v>60279</v>
+        <v>60280</v>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>超级慈悲</t>
+          <t>超级雷霆</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
@@ -4578,24 +4608,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>未实现</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>战斗中闪现或被召唤时，将回复主人最大生命28%的生命值，最大回复不超过目标等级*40（宠物等级低于角色等级时，回复效率将会出现衰减）</t>
+          <t>拥有用该技能的宠物，战斗中闪现或被召唤时，主人所有技能冷却回合-3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="n">
-        <v>60280</v>
+        <v>60281</v>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>超级雷霆</t>
+          <t>超级清心</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -4608,24 +4638,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>未实现</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>拥有用该技能的宠物，战斗中闪现或被召唤时，主人所有技能冷却回合-3</t>
+          <t>拥有用该技能的宠物，战斗中闪现或被召唤时，解除主人受到的控制状态，并附加控制免疫1~3回合</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="n">
-        <v>60281</v>
+        <v>60450</v>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>超级清心</t>
+          <t>组字秘</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -4635,27 +4665,27 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>生命+30000，伤害加成+15.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>仅属性（触发未实现）</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>拥有用该技能的宠物，战斗中闪现或被召唤时，解除主人受到的控制状态，并附加控制免疫1~3回合</t>
+          <t>九秘</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
-        <v>60450</v>
+        <v>67068</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>组字秘</t>
+          <t>修罗觉醒</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -4665,27 +4695,27 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>生命+30000，伤害加成+15.0%</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
+          <t>暴击+25.0%，物伤加成+20.0%，攻速%+10.0%，魔防%+20.0%</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>仅属性（触发未实现）</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>九秘</t>
+          <t>修罗觉醒</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
-        <v>67068</v>
+        <v>67077</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>修罗觉醒</t>
+          <t>战神护佑</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -4695,27 +4725,27 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>暴击+25.0%，物伤加成+20.0%，攻速%+10.0%，魔防%+20.0%</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
+          <t>攻速%+12.0%，魔攻%+10.0%，物防%+12.0%</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>仅属性（触发未实现）</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>修罗觉醒</t>
+          <t>战神护佑</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
-        <v>67077</v>
+        <v>67083</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>战神护佑</t>
+          <t>神牛意志</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -4725,27 +4755,27 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>攻速%+12.0%，魔攻%+10.0%，物防%+12.0%</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
+          <t>暴击+15.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>仅属性（触发未实现）</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>战神护佑</t>
+          <t>神牛意志</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
-        <v>67083</v>
+        <v>67097</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>神牛意志</t>
+          <t>神枭觉醒</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -4755,27 +4785,27 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>暴击+15.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
+          <t>暴击+20.0%，攻速%+15.0%，物攻%+15.0%，魔防%+20.0%</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>仅属性（触发未实现）</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>神牛意志</t>
+          <t>神枭觉醒</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>67097</v>
+        <v>67111</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>神枭觉醒</t>
+          <t>暗域</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -4785,27 +4815,27 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>暴击+20.0%，攻速%+15.0%，物攻%+15.0%，魔防%+20.0%</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>未实现</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>神枭觉醒</t>
+          <t>暗域</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
-        <v>67111</v>
+        <v>67133</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>暗域</t>
+          <t>神兔庇佑</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -4815,147 +4845,147 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>攻速%+15.0%，物攻%+15.0%，物防%+20.0%，魔防%+20.0%</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>仅属性（触发未实现）</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>暗域</t>
+          <t>神兔觉醒</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>67133</v>
+        <v>67200</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>神兔庇佑</t>
+          <t>阴阳怒焱</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>主动</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>攻速%+15.0%，物攻%+15.0%，物防%+20.0%，魔防%+20.0%</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
+          <t>魔法攻击(0)；目标2；倍率[1800]</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>部分（随机形态未做）</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>神兔觉醒</t>
+          <t>阴阳怒焱</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>67200</v>
+        <v>67207</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>阴阳怒焱</t>
+          <t>麒麟庇护</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>主动</t>
+          <t>被动</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>魔法攻击(0)；目标2；倍率[1800]</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>部分（随机形态未做）</t>
+          <t>暴击+20.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>仅属性（触发未实现）</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>阴阳怒焱</t>
+          <t>麒麟庇护</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>67207</v>
+        <v>67300</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>麒麟庇护</t>
+          <t>麒麟浴火</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>暴击+20.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
+          <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤3(每层10.0%，999回合)</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>部分（叠层已做，伤害分担未做）</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>麒麟庇护</t>
+          <t>麒麟浴火</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>67300</v>
+        <v>67310</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>麒麟浴火</t>
+          <t>筋斗云决</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>触发</t>
+          <t>被动</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤3(每层10.0%，999回合)</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>部分（叠层已做，伤害分担未做）</t>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>未实现</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>麒麟浴火</t>
+          <t>筋斗云决</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>67306</v>
+        <v>67331</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>仙泽福佑</t>
+          <t>死亡冲锋</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -4968,24 +4998,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>未实现</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>仙泽福佑</t>
+          <t>死亡冲锋</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>67310</v>
+        <v>67333</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>筋斗云决</t>
+          <t>战神圣体</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -4995,27 +5025,27 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>暴击+10.0%，攻速%+15.0%，物攻%+18.0%，魔防%+25.0%</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>仅属性（怒气未做）</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>筋斗云决</t>
+          <t>战神圣体</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>67331</v>
+        <v>67335</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>死亡冲锋</t>
+          <t>死亡追击</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -5028,24 +5058,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>未实现</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>死亡冲锋</t>
+          <t>死亡追击</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>67333</v>
+        <v>67342</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>战神圣体</t>
+          <t>玄女圣体</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -5055,7 +5085,7 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>暴击+10.0%，攻速%+15.0%，物攻%+18.0%，魔防%+25.0%</t>
+          <t>暴击+15.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -5065,17 +5095,17 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>战神圣体</t>
+          <t>玄女圣体</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>67335</v>
+        <v>67345</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>死亡追击</t>
+          <t>天佑</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -5088,24 +5118,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>未实现</t>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>未实现（伤害分担）</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>死亡追击</t>
+          <t>天佑</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
-        <v>67340</v>
+        <v>67347</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>玄天暴</t>
+          <t>初音圣体</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -5115,62 +5145,62 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>魔法暴击+20.0%，攻速%+18.0%，魔攻%+15.0%，物防%+25.0%</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>仅属性（触发未实现）</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>玄天暴</t>
+          <t>初音圣体</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
-        <v>67342</v>
+        <v>67353</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>玄女圣体</t>
+          <t>封阳击</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>主动</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>暴击+15.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%</t>
+          <t>物穿(0)；目标1；倍率[260, 260, 260, 260, 260]；5段</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>仅属性（怒气未做）</t>
+          <t>部分（击杀转火未做）</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>玄女圣体</t>
+          <t>封阳击</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
-        <v>67345</v>
+        <v>67361</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>天佑</t>
+          <t>搬山</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>护盾</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
@@ -5178,114 +5208,114 @@
           <t>无</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>未实现（伤害分担）</t>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>未实现</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>天佑</t>
+          <t>搬山</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>67347</v>
+        <v>67363</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>初音圣体</t>
+          <t>死亡镰刀</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>主动</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>魔法暴击+20.0%，攻速%+18.0%，魔攻%+15.0%，物防%+25.0%</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
+          <t>魔法攻击(0)；目标1；倍率[260, 260, 260, 260, 260]；5段</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>部分（击杀转火未做）</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>初音圣体</t>
+          <t>死亡镰刀</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
-        <v>67353</v>
+        <v>67367</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>封阳击</t>
+          <t>死神神体</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>主动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>物穿(0)；目标1；倍率[260, 260, 260, 260, 260]；5段</t>
+          <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；法穿(300)；目标1；倍率[1000]</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>部分（击杀转火未做）</t>
+          <t>部分（属性/法穿已做，怒气未做）</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>封阳击</t>
+          <t>死神神体</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
-        <v>67361</v>
+        <v>67368</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>搬山</t>
+          <t>无忧击</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>护盾</t>
+          <t>主动</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>物理攻击(暴击吸血)(0)；目标4；倍率[466, 466, 468]；3段</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>部分（附加治疗/护盾未做）</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>搬山</t>
+          <t>无忧击</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
-        <v>67363</v>
+        <v>67378</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>死亡镰刀</t>
+          <t>乾坤天降</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -5295,112 +5325,22 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>魔法攻击(0)；目标1；倍率[260, 260, 260, 260, 260]；5段</t>
+          <t>物理攻击(暴击吸血)(0)；目标6；倍率[1200]</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>部分（击杀转火未做）</t>
+          <t>部分（溅射近似）</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>死亡镰刀</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="n">
-        <v>67367</v>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>死神神体</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；法穿(300)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>部分（属性/法穿已做，怒气未做）</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>死神神体</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="n">
-        <v>67368</v>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>无忧击</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>主动</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>物理攻击(暴击吸血)(0)；目标4；倍率[466, 466, 468]；3段</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>部分（附加治疗/护盾未做）</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>无忧击</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="n">
-        <v>67378</v>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>乾坤天降</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>主动</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>物理攻击(暴击吸血)(0)；目标6；倍率[1200]</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>部分（溅射近似）</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
           <t>乾坤·天降</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F29"/>
+  <autoFilter ref="A1:F26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'详细表'!$A$1:$F$120</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待补-部分'!$A$1:$F$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待补-部分'!$A$1:$F$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -634,7 +634,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>独立脚本（攻击扣蓝10%；蓝耗+25%未做）</t>
+          <t>独立脚本（召唤清心+控制免疫）</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -642,9 +642,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>近似（封心+护盾已接）</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>独立脚本（攻击扣蓝10%；蓝耗+25%未做）</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -652,9 +652,9 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>独立脚本（攻击扣蓝15%）</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>近似（封心+护盾已接）</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -662,9 +662,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>近似（20%暴击吸血）</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>独立脚本（攻击扣蓝15%）</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -672,9 +672,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>独立脚本（真实伤害）</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>近似（20%暴击吸血）</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -684,7 +684,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>独立脚本（物理受击护盾）</t>
+          <t>独立脚本（真实伤害）</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -692,9 +692,9 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>近似（群增伤20%）</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>独立脚本（物理受击护盾）</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -702,9 +702,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>独立脚本（出场盾+受击魔法盾）</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>近似（群增伤20%）</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -714,7 +714,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>精确（当前生命25%脚本）</t>
+          <t>独立脚本（出场盾+受击魔法盾）</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -722,9 +722,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>部分（随机形态未做）</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>精确（当前生命25%脚本）</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -734,7 +734,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>部分（叠层已做，伤害分担未做）</t>
+          <t>部分（随机形态未做）</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -742,9 +742,9 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>独立脚本（减伤/反伤/沉默）</t>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>部分（叠层已做，伤害分担未做）</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -754,7 +754,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>独立脚本（死亡回全队40%生命）</t>
+          <t>独立脚本（减伤/反伤/沉默）</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -762,9 +762,9 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>近似（50%暴击吸血）</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>独立脚本（死亡回全队40%生命）</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -772,9 +772,9 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>近似（10%法术吸血）</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>独立脚本（速度条件增伤/减伤）</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -782,9 +782,9 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>独立脚本（随机双/三倍+速度增伤）</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>近似（50%暴击吸血）</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -794,7 +794,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>近似（护盾+10%免疫）</t>
+          <t>近似（10%法术吸血）</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -802,9 +802,9 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>未实现（伤害分担）</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>独立脚本（随机双/三倍+速度增伤）</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -812,9 +812,9 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>独立脚本（25%法术吸血+受击减伤）</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>近似（护盾+10%免疫）</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -822,9 +822,9 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>独立脚本（击杀回血+燃火增伤）</t>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>未实现（伤害分担）</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -832,9 +832,9 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>部分（属性/法穿已做，怒气未做）</t>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>独立脚本（25%法术吸血+受击减伤）</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -842,9 +842,9 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>部分（附加治疗/护盾未做）</t>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>独立脚本（击杀回血+燃火增伤）</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -854,57 +854,77 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>部分（溅射近似）</t>
+          <t>部分（属性/法穿已做，怒气未做）</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>部分（附加治疗/护盾未做）</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>部分（溅射近似）</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>独立脚本：700001-700005 等专用脚本</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>精确：属性/公式按说明落表</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>近似：属性/目标/消耗准确，伤害倍率或 buff 参数推断</t>
+          <t>独立脚本：700001-700005 等专用脚本</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>部分：部分机制已做，剩余机制未做</t>
+          <t>精确：属性/公式按说明落表</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>未实现：目前没有生效记录</t>
+          <t>近似：属性/目标/消耗准确，伤害倍率或 buff 参数推断</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
+        <is>
+          <t>部分：部分机制已做，剩余机制未做</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>未实现：目前没有生效记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>伤害倍率无法从客户端取得，均为推断值</t>
         </is>
@@ -1035,17 +1055,17 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>召唤清心+控制免疫；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>独立脚本（召唤清心+控制免疫）</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
@@ -3075,17 +3095,17 @@
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>速度条件增伤/减伤；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>独立脚本（速度条件增伤/减伤）</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr">
@@ -4546,7 +4566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4621,11 +4641,11 @@
     </row>
     <row r="3">
       <c r="A3" s="9" t="n">
-        <v>60281</v>
+        <v>60450</v>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>超级清心</t>
+          <t>组字秘</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -4635,27 +4655,27 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>生命+30000，伤害加成+15.0%</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>仅属性（触发未实现）</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>拥有用该技能的宠物，战斗中闪现或被召唤时，解除主人受到的控制状态，并附加控制免疫1~3回合</t>
+          <t>九秘</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="n">
-        <v>60450</v>
+        <v>67068</v>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>组字秘</t>
+          <t>修罗觉醒</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -4665,7 +4685,7 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>生命+30000，伤害加成+15.0%</t>
+          <t>暴击+25.0%，物伤加成+20.0%，攻速%+10.0%，魔防%+20.0%</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -4675,17 +4695,17 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>九秘</t>
+          <t>修罗觉醒</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
-        <v>67068</v>
+        <v>67077</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>修罗觉醒</t>
+          <t>战神护佑</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -4695,7 +4715,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>暴击+25.0%，物伤加成+20.0%，攻速%+10.0%，魔防%+20.0%</t>
+          <t>攻速%+12.0%，魔攻%+10.0%，物防%+12.0%</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -4705,17 +4725,17 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>修罗觉醒</t>
+          <t>战神护佑</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
-        <v>67077</v>
+        <v>67083</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>战神护佑</t>
+          <t>神牛意志</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -4725,7 +4745,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>攻速%+12.0%，魔攻%+10.0%，物防%+12.0%</t>
+          <t>暴击+15.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -4735,17 +4755,17 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>战神护佑</t>
+          <t>神牛意志</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
-        <v>67083</v>
+        <v>67097</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>神牛意志</t>
+          <t>神枭觉醒</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -4755,7 +4775,7 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>暴击+15.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
+          <t>暴击+20.0%，攻速%+15.0%，物攻%+15.0%，魔防%+20.0%</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -4765,17 +4785,17 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>神牛意志</t>
+          <t>神枭觉醒</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
-        <v>67097</v>
+        <v>67111</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>神枭觉醒</t>
+          <t>暗域</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -4785,27 +4805,27 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>暴击+20.0%，攻速%+15.0%，物攻%+15.0%，魔防%+20.0%</t>
+          <t>无</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>仅属性（触发未实现）</t>
+          <t>未实现</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>神枭觉醒</t>
+          <t>暗域</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>67111</v>
+        <v>67133</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>暗域</t>
+          <t>神兔庇佑</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -4815,147 +4835,147 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>攻速%+15.0%，物攻%+15.0%，物防%+20.0%，魔防%+20.0%</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>仅属性（触发未实现）</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>暗域</t>
+          <t>神兔觉醒</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
-        <v>67133</v>
+        <v>67200</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>神兔庇佑</t>
+          <t>阴阳怒焱</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>主动</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>攻速%+15.0%，物攻%+15.0%，物防%+20.0%，魔防%+20.0%</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
+          <t>魔法攻击(0)；目标2；倍率[1800]</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>部分（随机形态未做）</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>神兔觉醒</t>
+          <t>阴阳怒焱</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>67200</v>
+        <v>67207</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>阴阳怒焱</t>
+          <t>麒麟庇护</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>主动</t>
+          <t>被动</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>魔法攻击(0)；目标2；倍率[1800]</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>部分（随机形态未做）</t>
+          <t>暴击+20.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>仅属性（触发未实现）</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>阴阳怒焱</t>
+          <t>麒麟庇护</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>67207</v>
+        <v>67300</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>麒麟庇护</t>
+          <t>麒麟浴火</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>暴击+20.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
+          <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤3(每层10.0%，999回合)</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>部分（叠层已做，伤害分担未做）</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>麒麟庇护</t>
+          <t>麒麟浴火</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>67300</v>
+        <v>67331</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>麒麟浴火</t>
+          <t>死亡冲锋</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>触发</t>
+          <t>被动</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤3(每层10.0%，999回合)</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>部分（叠层已做，伤害分担未做）</t>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>未实现</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>麒麟浴火</t>
+          <t>死亡冲锋</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>67310</v>
+        <v>67333</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>筋斗云决</t>
+          <t>战神圣体</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -4965,27 +4985,27 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>暴击+10.0%，攻速%+15.0%，物攻%+18.0%，魔防%+25.0%</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>仅属性（怒气未做）</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>筋斗云决</t>
+          <t>战神圣体</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>67331</v>
+        <v>67335</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>死亡冲锋</t>
+          <t>死亡追击</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -5005,17 +5025,17 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>死亡冲锋</t>
+          <t>死亡追击</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>67333</v>
+        <v>67342</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>战神圣体</t>
+          <t>玄女圣体</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -5025,7 +5045,7 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>暴击+10.0%，攻速%+15.0%，物攻%+18.0%，魔防%+25.0%</t>
+          <t>暴击+15.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
@@ -5035,17 +5055,17 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>战神圣体</t>
+          <t>玄女圣体</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>67335</v>
+        <v>67345</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>死亡追击</t>
+          <t>天佑</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -5060,22 +5080,22 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>未实现（伤害分担）</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>死亡追击</t>
+          <t>天佑</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>67342</v>
+        <v>67347</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>玄女圣体</t>
+          <t>初音圣体</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -5085,87 +5105,87 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>暴击+15.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>仅属性（怒气未做）</t>
+          <t>魔法暴击+20.0%，攻速%+18.0%，魔攻%+15.0%，物防%+25.0%</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>仅属性（触发未实现）</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>玄女圣体</t>
+          <t>初音圣体</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>67345</v>
+        <v>67353</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>天佑</t>
+          <t>封阳击</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>主动</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>未实现（伤害分担）</t>
+          <t>物穿(0)；目标1；倍率[260, 260, 260, 260, 260]；5段</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>部分（击杀转火未做）</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>天佑</t>
+          <t>封阳击</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
-        <v>67347</v>
+        <v>67361</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>初音圣体</t>
+          <t>搬山</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>护盾</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>魔法暴击+20.0%，攻速%+18.0%，魔攻%+15.0%，物防%+25.0%</t>
+          <t>无</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>仅属性（触发未实现）</t>
+          <t>未实现</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>初音圣体</t>
+          <t>搬山</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
-        <v>67353</v>
+        <v>67363</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>封阳击</t>
+          <t>死亡镰刀</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -5175,7 +5195,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>物穿(0)；目标1；倍率[260, 260, 260, 260, 260]；5段</t>
+          <t>魔法攻击(0)；目标1；倍率[260, 260, 260, 260, 260]；5段</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -5185,47 +5205,47 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>封阳击</t>
+          <t>死亡镰刀</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
-        <v>67361</v>
+        <v>67367</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>搬山</t>
+          <t>死神神体</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>护盾</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；法穿(300)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>部分（属性/法穿已做，怒气未做）</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>搬山</t>
+          <t>死神神体</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>67363</v>
+        <v>67368</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>死亡镰刀</t>
+          <t>无忧击</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -5235,112 +5255,52 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>魔法攻击(0)；目标1；倍率[260, 260, 260, 260, 260]；5段</t>
+          <t>物理攻击(暴击吸血)(0)；目标4；倍率[466, 466, 468]；3段</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>部分（击杀转火未做）</t>
+          <t>部分（附加治疗/护盾未做）</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>死亡镰刀</t>
+          <t>无忧击</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
-        <v>67367</v>
+        <v>67378</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>死神神体</t>
+          <t>乾坤天降</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>触发</t>
+          <t>主动</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；法穿(300)；目标1；倍率[1000]</t>
+          <t>物理攻击(暴击吸血)(0)；目标6；倍率[1200]</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>部分（属性/法穿已做，怒气未做）</t>
+          <t>部分（溅射近似）</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>死神神体</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="n">
-        <v>67368</v>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>无忧击</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>主动</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>物理攻击(暴击吸血)(0)；目标4；倍率[466, 466, 468]；3段</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>部分（附加治疗/护盾未做）</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>无忧击</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="n">
-        <v>67378</v>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>乾坤天降</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>主动</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>物理攻击(暴击吸血)(0)；目标6；倍率[1200]</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>部分（溅射近似）</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
           <t>乾坤·天降</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F26"/>
+  <autoFilter ref="A1:F24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'详细表'!$A$1:$F$120</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待补-部分'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待补-部分'!$A$1:$F$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>魔法攻击(0)；目标2；倍率[1800]</t>
-        </is>
-      </c>
-      <c r="E62" s="12" t="inlineStr">
-        <is>
-          <t>部分（随机形态未做）</t>
+          <t>随机阳/阴形态()；目标1；倍率[1800]</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>独立脚本（40%阳焱全体+灼烧5%；60%阴焱2目标×2+50%眩晕）</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4507,41 +4507,41 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>67200</v>
+        <v>67207</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>阴阳怒焱</t>
+          <t>麒麟庇护</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>主动</t>
+          <t>被动</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>魔法攻击(0)；目标2；倍率[1800]</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>部分（随机形态未做）</t>
+          <t>暴击+20.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>仅属性（触发未实现）</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>阴阳怒焱</t>
+          <t>麒麟庇护</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
-        <v>67207</v>
+        <v>67347</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>麒麟庇护</t>
+          <t>初音圣体</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>暴击+20.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
+          <t>魔法暴击+20.0%，攻速%+18.0%，魔攻%+15.0%，物防%+25.0%</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -4561,47 +4561,47 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>麒麟庇护</t>
+          <t>初音圣体</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>67347</v>
+        <v>67353</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>初音圣体</t>
+          <t>封阳击</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>主动</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>魔法暴击+20.0%，攻速%+18.0%，魔攻%+15.0%，物防%+25.0%</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
+          <t>物穿(0)；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>部分（5段固定；击杀后自动转火已生效）</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>初音圣体</t>
+          <t>封阳击</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
-        <v>67353</v>
+        <v>67363</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>封阳击</t>
+          <t>死亡镰刀</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>物穿(0)；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
+          <t>魔法攻击(0)；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -4621,102 +4621,72 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>封阳击</t>
+          <t>死亡镰刀</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>67363</v>
+        <v>67367</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>死亡镰刀</t>
+          <t>死神神体</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>主动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>魔法攻击(0)；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
+          <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；法穿(300)；目标1；倍率[1000]</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>部分（5段固定；击杀后自动转火已生效）</t>
+          <t>部分（属性/法穿已做；阵亡单位增伤/魔防未做）</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>死亡镰刀</t>
+          <t>死神神体</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
-        <v>67367</v>
+        <v>67378</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>死神神体</t>
+          <t>乾坤天降</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>触发</t>
+          <t>主动</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；法穿(300)；目标1；倍率[1000]</t>
+          <t>物理攻击(暴击吸血)(0)；目标6；倍率[1200]</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>部分（属性/法穿已做；阵亡单位增伤/魔防未做）</t>
+          <t>部分（相邻6目标同倍率溅射）</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>死神神体</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>67378</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>乾坤天降</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>主动</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>物理攻击(暴击吸血)(0)；目标6；倍率[1200]</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>部分（相邻6目标同倍率溅射）</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
           <t>乾坤·天降</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'详细表'!$A$1:$F$120</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待补-部分'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待补-部分'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -42,7 +42,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,11 +67,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,9 +114,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -557,7 +549,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
@@ -577,7 +569,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -587,7 +579,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -600,7 +592,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>独立脚本：700001-700022 专用脚本</t>
+          <t>独立脚本：700001-700031 专用脚本</t>
         </is>
       </c>
     </row>
@@ -866,12 +858,12 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>攻击扣蓝；目标1；倍率[1000]</t>
+          <t>攻击扣蓝+蓝耗25%；目标1；倍率[1000]</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>独立脚本（攻击扣蓝10%；蓝耗+25%未做）</t>
+          <t>独立脚本（攻击扣蓝10%；蓝耗+25%已生效）</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -1431,17 +1423,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>生命+30000，伤害加成+15.0%</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
+          <t>生命+30000，伤害加成+15.0%；攻击触发伤害分担；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>独立脚本（攻击30%触发40%伤害分担2回合；属性已生效）</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -1611,17 +1603,17 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>暴击+25.0%，物伤加成+20.0%，攻速%+10.0%，魔防%+20.0%</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
+          <t>暴击+25.0%，物伤加成+20.0%，攻速%+10.0%，魔防%+20.0%；回合末清异常()；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>独立脚本（回合末50%清除自身异常）</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -1731,17 +1723,17 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>攻速%+12.0%，魔攻%+10.0%，物防%+12.0%</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
+          <t>攻速%+12.0%，魔攻%+10.0%，物防%+12.0%；击杀回血()；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>独立脚本（击杀回复10%最大生命）</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -1851,17 +1843,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>暴击+15.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
+          <t>暴击+15.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%；攻击清增益；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>独立脚本（每次出手清除目标1个增益）</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -2031,17 +2023,17 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>暴击+20.0%，攻速%+15.0%，物攻%+15.0%，魔防%+20.0%</t>
-        </is>
-      </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
+          <t>暴击+20.0%，攻速%+15.0%，物攻%+15.0%，魔防%+20.0%；首次受击增伤()；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>独立脚本（首次受击未死+20%物伤，本回合）</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -2481,17 +2473,17 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>攻速%+15.0%，物攻%+15.0%，物防%+20.0%，魔防%+20.0%</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
+          <t>攻速%+15.0%，物攻%+15.0%，物防%+20.0%，魔防%+20.0%；首次受击增伤+免伤盾()；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>独立脚本（首次受击+20%物伤；受击30%几率30%减伤3回合）</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -2541,17 +2533,17 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>触发</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>暴击+20.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
+          <t>暴击+20.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%；攻击清增益；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>独立脚本（30%几率清除目标1个增益）</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -3481,7 +3473,7 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>仅属性（触发未实现）</t>
+          <t>仅属性（需受击前伤害值；引擎无该hook，未做）</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
@@ -3599,9 +3591,9 @@
           <t>物穿(0)；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
         </is>
       </c>
-      <c r="E98" s="12" t="inlineStr">
-        <is>
-          <t>部分（5段固定；击杀后自动转火已生效）</t>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>独立脚本（5–8段随机；击杀后自动转火）</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
@@ -3899,9 +3891,9 @@
           <t>魔法攻击(0)；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
         </is>
       </c>
-      <c r="E108" s="12" t="inlineStr">
-        <is>
-          <t>部分（5段固定；击杀后自动转火已生效）</t>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>独立脚本（5–8段随机；击杀后自动转火；每段20%眩晕2回合）</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr">
@@ -4016,12 +4008,12 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；法穿(300)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E112" s="12" t="inlineStr">
-        <is>
-          <t>部分（属性/法穿已做；阵亡单位增伤/魔防未做）</t>
+          <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；无视防御+阵亡增伤()；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>独立脚本（攻击人物无视30%防；每个阵亡友方+10%伤害/+20%魔防）</t>
         </is>
       </c>
       <c r="F112" s="8" t="inlineStr">
@@ -4199,9 +4191,9 @@
           <t>物理攻击(暴击吸血)(0)；目标6；倍率[1200]</t>
         </is>
       </c>
-      <c r="E118" s="12" t="inlineStr">
-        <is>
-          <t>部分（相邻6目标同倍率溅射）</t>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>部分（主目标+相邻5目标同倍率；风雷护盾触发未做；15%速度加成未落表）</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
@@ -4282,7 +4274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4327,11 +4319,11 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>60450</v>
+        <v>67347</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>组字秘</t>
+          <t>初音圣体</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -4341,352 +4333,52 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>生命+30000，伤害加成+15.0%</t>
+          <t>魔法暴击+20.0%，攻速%+18.0%，魔攻%+15.0%，物防%+25.0%</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>仅属性（触发未实现）</t>
+          <t>仅属性（需受击前伤害值；引擎无该hook，未做）</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>九秘</t>
+          <t>初音圣体</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>67068</v>
+        <v>67378</v>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>修罗觉醒</t>
+          <t>乾坤天降</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>主动</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>暴击+25.0%，物伤加成+20.0%，攻速%+10.0%，魔防%+20.0%</t>
+          <t>物理攻击(暴击吸血)(0)；目标6；倍率[1200]</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>仅属性（触发未实现）</t>
+          <t>部分（主目标+相邻5目标同倍率；风雷护盾触发未做；15%速度加成未落表）</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>修罗觉醒</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="n">
-        <v>67077</v>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>战神护佑</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>被动</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>攻速%+12.0%，魔攻%+10.0%，物防%+12.0%</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>战神护佑</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>67083</v>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>神牛意志</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>被动</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>暴击+15.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>神牛意志</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>67097</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>神枭觉醒</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>被动</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>暴击+20.0%，攻速%+15.0%，物攻%+15.0%，魔防%+20.0%</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>神枭觉醒</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>67133</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>神兔庇佑</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>被动</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>攻速%+15.0%，物攻%+15.0%，物防%+20.0%，魔防%+20.0%</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>神兔觉醒</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>67207</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>麒麟庇护</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>被动</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>暴击+20.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>麒麟庇护</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>67347</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>初音圣体</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>被动</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>魔法暴击+20.0%，攻速%+18.0%，魔攻%+15.0%，物防%+25.0%</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（触发未实现）</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>初音圣体</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>67353</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>封阳击</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>主动</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>物穿(0)；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>部分（5段固定；击杀后自动转火已生效）</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>封阳击</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>67363</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>死亡镰刀</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>主动</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>魔法攻击(0)；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>部分（5段固定；击杀后自动转火已生效）</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>死亡镰刀</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>67367</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>死神神体</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；法穿(300)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>部分（属性/法穿已做；阵亡单位增伤/魔防未做）</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>死神神体</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>67378</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>乾坤天降</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>主动</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>物理攻击(暴击吸血)(0)；目标6；倍率[1200]</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>部分（相邻6目标同倍率溅射）</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
           <t>乾坤·天降</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F13"/>
+  <autoFilter ref="A1:F3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'详细表'!$A$1:$F$120</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待补-部分'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待补-部分'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -42,7 +42,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,11 +62,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,13 +91,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -114,9 +108,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -484,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -549,7 +540,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -562,77 +553,57 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>仅属性</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-    </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>部分</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>独立脚本：700001-700033 专用脚本</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>说明</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>精确：属性/公式按说明落表</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>独立脚本：700001-700031 专用脚本</t>
+          <t>近似：属性/目标/消耗准确，伤害倍率或 buff 参数推断</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>精确：属性/公式按说明落表</t>
+          <t>部分：部分机制已做，剩余机制未做</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>近似：属性/目标/消耗准确，伤害倍率或 buff 参数推断</t>
+          <t>未实现：目前没有生效记录</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>部分：部分机制已做，剩余机制未做</t>
+          <t>独立脚本均已编译、差分校验并热加载，战斗内触发仍建议实战确认</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
-        <is>
-          <t>未实现：目前没有生效记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>独立脚本均已编译、差分校验并热加载，战斗内触发仍建议实战确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
         <is>
           <t>伤害倍率无法从客户端取得，均为推断值</t>
         </is>
@@ -661,3602 +632,3602 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>当前效果</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>技能说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="n">
+      <c r="A2" s="7" t="n">
         <v>60279</v>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>超级慈悲</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>召唤回主人血；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>独立脚本（召唤回主人28%生命）</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>战斗中闪现或被召唤时，将回复主人最大生命28%的生命值，最大回复不超过目标等级*40（宠物等级低于角色等级时，回复效率将会出现衰减）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="7" t="n">
         <v>60280</v>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>超级雷霆</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>召唤减主人冷却；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>独立脚本（召唤时主人技能冷却-3）</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>拥有用该技能的宠物，战斗中闪现或被召唤时，主人所有技能冷却回合-3</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="7" t="n">
         <v>60281</v>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>超级清心</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>召唤清心+控制免疫；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>独立脚本（召唤清心+控制免疫）</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>拥有用该技能的宠物，战斗中闪现或被召唤时，解除主人受到的控制状态，并附加控制免疫1~3回合</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="7" t="n">
         <v>60282</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>超级护主</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>脚本32000(610, 550, 1000)；目标1；倍率[1000]；CD1</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>当主人受到伤害时，有61%几率为主人承担55%伤害</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>60283</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>超级涅槃</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>脚本32001(400, 350, 0, 75)；目标1；倍率[1000]；CD4</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>主人死亡后有40%的几率将其复活，并恢复35%的生命,最大回复不超过主人等级*75</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="7" t="n">
         <v>60284</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>超级破魔</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>攻击扣蓝+蓝耗25%；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>独立脚本（攻击扣蓝10%；蓝耗+25%已生效）</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>拥有该技能的宠物蓝耗增加25%，每次攻击将使目标减少最大值10%的魔法值，同个单位一回合内受到多次破魔时效果会降低</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>60285</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>超级神佑</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>神佑(140, 180, 220, 280, 1000, 0)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>死亡后有28%概率复活并恢复100%生命，与鬼魂、高级鬼魂共存时高级神佑技能无效，体质加点越低触发几率越高</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="7" t="n">
         <v>60286</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>超级逃生</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>逃生(490, 0, 150)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>受到致命伤害时有49%几率回复150点生命</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>60288</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>超级反弹</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>反弹(350, 650)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>受到攻击时有35%的几率反弹65%的伤害给目标</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="7" t="n">
         <v>60290</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>超级魔法还击</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>还击(580, [60011, 60012, 60013)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>受击近战攻击时有58%概率以魔法还击对方</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <v>60291</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>超级报复</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>物理攻击(500, 300, 100)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>生命值低于58%时，当生命值越低时所造成的伤害越高</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="7" t="n">
         <v>60301</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>超级审判</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>审判(350)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>对拥有神佑、逃生的敌人伤害结果增加35%，同时击杀敌人时，敌人无法触发神佑效果（可触发逃生）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="7" t="n">
         <v>60302</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>超级驱鬼</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>驱鬼(1000, 80)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>对带有鬼魂的怪物造成2倍伤害，并无视目标8%物理防御，若击杀可将其打出战斗场景外</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="7" t="n">
         <v>60304</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>超级物攻祝福</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>脚本31000(380)；目标1；倍率[1000]；buff:物攻祝福(2回合)</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>回合初有38%概率为主人提升10%物攻，不占用出手回合，持续2回合</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="7" t="n">
         <v>60308</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>超级强体</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>生命=等级×55.0+380</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>永久提升宠物等级×55+380的生命值</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="7" t="n">
         <v>60311</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>超级逆击</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>逆击(330)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>对身上有祝福类状态的目标额外造成33%的伤害</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="7" t="n">
         <v>60312</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>超级敏捷</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>攻速%+15.0%</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>永久提升15%攻速</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="7" t="n">
         <v>60313</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>超级防御</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>物防=等级×12.0+88</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>永久提升等级×12+88物防</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="7" t="n">
         <v>60314</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>超级魔法防御</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>魔防=等级×12.0+88</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>永久提升等级×12+88魔防</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="7" t="n">
         <v>60326</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>超级强击</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>命中+140；强击(150, 1700, 650)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>对宠物单位伤害增加15%，若目标最大生命值超过己方1.7倍，额外造成65%的伤害</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="7" t="n">
         <v>60444</v>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>兵字秘</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>物穿(400)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>九秘</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="7" t="n">
         <v>60447</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>斗字秘</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>生命%+5.0%，魔攻%+3.0%；法术连击；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>九秘</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="7" t="n">
         <v>60448</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>行字秘</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>闪避+100，攻速%+35.0%</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>九秘</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="7" t="n">
         <v>60449</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>灵魂冲击</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>攻速%+20.0%；眩晕(800, 800, 800, 800)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>灵魂冲击</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="7" t="n">
         <v>60450</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>组字秘</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>生命+30000，伤害加成+15.0%；攻击触发伤害分担；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>独立脚本（攻击30%触发40%伤害分担2回合；属性已生效）</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>九秘</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="7" t="n">
         <v>60590</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>灵魂超度</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>魔攻%+20.0%；魔法攻击(0)；目标4；倍率[1800]</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>对生命值低于50%的目标造成2倍魔法伤害，若目标生命值超过50%，则造成150%的魔法伤害，永久提升20%魔攻</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="7" t="n">
         <v>60603</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>枭刃</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>物穿(0)；目标1×2；倍率[700, 700]；2段</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>枭刃</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="7" t="n">
         <v>61064</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>法术吸血</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>吸血(1000, 150)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>法术吸血</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="7" t="n">
         <v>67038</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>魔气入体</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>禁魂(1000, 1000)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>魔气入体</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n">
+      <c r="A31" s="7" t="n">
         <v>67067</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>魔域</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>暴伤+40.0%</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>魔域</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n">
+      <c r="A32" s="7" t="n">
         <v>67068</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>修罗觉醒</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>暴击+25.0%，物伤加成+20.0%，攻速%+10.0%，魔防%+20.0%；回合末清异常()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>独立脚本（回合末50%清除自身异常）</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>修罗觉醒</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="7" t="n">
         <v>67074</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>推气过穴</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>治疗(80, 200)；目标3；倍率[1000]；buff:持续回血(每回合5.0%，3回合)</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>近似（治疗/护盾参数）</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>推气过穴</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n">
+      <c r="A34" s="7" t="n">
         <v>67075</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>郎神共舞</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>魔法攻击(0)；目标3；倍率[1600]；MP99；buff:生命护盾(生命上限200.0%，2回合)、封心(封心50.0%，2回合)</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>近似（封心+护盾已接）</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>郎神共舞</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="n">
+      <c r="A35" s="7" t="n">
         <v>67076</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>神猿庇佑</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>生命%+30.0%，攻速%+15.0%，物防%+25.0%，魔防%+25.0%</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>神猿庇佑</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n">
+      <c r="A36" s="7" t="n">
         <v>67077</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>战神护佑</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>攻速%+12.0%，魔攻%+10.0%，物防%+12.0%；击杀回血()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>独立脚本（击杀回复10%最大生命）</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>战神护佑</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="n">
+      <c r="A37" s="7" t="n">
         <v>67080</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>炸蓝</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>攻击扣蓝；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>独立脚本（攻击扣蓝15%）</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>炸蓝</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="n">
+      <c r="A38" s="7" t="n">
         <v>67081</v>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>神威</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>暴伤+20.0%；法术连击；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>神威</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="n">
+      <c r="A39" s="7" t="n">
         <v>67082</v>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>牛威</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤99(每层10.0%，999回合)</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>牛威</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="n">
+      <c r="A40" s="7" t="n">
         <v>67083</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>神牛意志</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>暴击+15.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%；攻击清增益；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>独立脚本（每次出手清除目标1个增益）</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>神牛意志</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="n">
+      <c r="A41" s="7" t="n">
         <v>67085</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>天诛</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>物理攻击(暴击吸血)(200)；目标4；倍率[1800]</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>近似（20%暴击吸血）</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>天诛</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="n">
+      <c r="A42" s="7" t="n">
         <v>67086</v>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>神兵护佑</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>攻速%+12.0%，物防%+12.0%，魔防%+15.0%</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>神兵护佑</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="n">
+      <c r="A43" s="7" t="n">
         <v>67087</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>神兵加持</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>连击(500, 0, 1800, 1800)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>神兵加持</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="n">
+      <c r="A44" s="7" t="n">
         <v>67091</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>白灵祝福</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>生命%+35.0%，攻速%+18.0%，物防%+30.0%，魔防%+30.0%；被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，2回合)</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>白灵祝福</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="n">
+      <c r="A45" s="7" t="n">
         <v>67093</v>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>神猿加持</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，2回合)、反伤(20.0%反伤，999回合)</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>神猿加持</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="n">
+      <c r="A46" s="7" t="n">
         <v>67097</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>神枭觉醒</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>暴击+20.0%，攻速%+15.0%，物攻%+15.0%，魔防%+20.0%；首次受击增伤()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>独立脚本（首次受击未死+20%物伤，本回合）</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>神枭觉醒</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="n">
+      <c r="A47" s="7" t="n">
         <v>67110</v>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>君皇横斩</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>真实伤害(500)；目标4；倍率[1800]</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
         <is>
           <t>独立脚本（真实伤害）</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>君皇横斩</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="n">
+      <c r="A48" s="7" t="n">
         <v>67111</v>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>暗域</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>物伤加成+10.0%，物攻%+20.0%；同宠增伤；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t>独立脚本（同阵营暗夜君王每只+5%横斩伤害，上限20%；另+10%物伤+20%物攻）</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>暗域</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="n">
+      <c r="A49" s="7" t="n">
         <v>67112</v>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>君王体魄</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>攻速%+12.0%，物攻%+15.0%，物防%+12.0%</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>君王体魄：</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="n">
+      <c r="A50" s="7" t="n">
         <v>67113</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>生命化泉</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>治疗(120, 200)；目标4；倍率[1000]；buff:持续回血(每回合8.0%，3回合)</t>
         </is>
       </c>
-      <c r="E50" s="10" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>近似（治疗/护盾参数）</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>生命化泉</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="n">
+      <c r="A51" s="7" t="n">
         <v>67114</v>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>炼气化神</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>回蓝(300, 0)；目标5；倍率[1000]；MP3</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>近似（治疗/护盾参数）</t>
         </is>
       </c>
-      <c r="F51" s="8" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>炼气化神</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="n">
+      <c r="A52" s="7" t="n">
         <v>67115</v>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>换天之术</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，2回合)、反伤(20.0%反伤，999回合)</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>换天之术</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="n">
+      <c r="A53" s="7" t="n">
         <v>67116</v>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>冥王庇佑</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>生命%+30.0%，攻速%+20.0%，物防%+25.0%，魔防%+25.0%；物理受击护盾(200, 300, 2)；目标1；倍率[1000]；CD1</t>
         </is>
       </c>
-      <c r="E53" s="9" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>独立脚本（物理受击护盾）</t>
         </is>
       </c>
-      <c r="F53" s="8" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>神猿庇佑</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="n">
+      <c r="A54" s="7" t="n">
         <v>67117</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>罗汉金钟</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>纯 buff；目标13；倍率[1000]；MP4；CD2；buff:减伤(50.0%减伤，3回合)</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
         <is>
           <t>近似（治疗/护盾参数）</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>罗汉金钟</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="n">
+      <c r="A55" s="7" t="n">
         <v>67118</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>菩提明镜</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>纯 buff；目标1；倍率[1000]；buff:反伤(35.0%反伤，3回合)</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>近似（治疗/护盾参数）</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>菩提明镜</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="n">
+      <c r="A56" s="7" t="n">
         <v>67119</v>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>燃烧之光</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>纯 buff；目标13；倍率[1000]；MP4；CD2；buff:增伤(20.0%增伤，3回合)</t>
         </is>
       </c>
-      <c r="E56" s="10" t="inlineStr">
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t>近似（群增伤20%）</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>燃烧之光</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="n">
+      <c r="A57" s="7" t="n">
         <v>67127</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>剑尊庇佑</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>生命%+30.0%，攻速%+20.0%，物防%+25.0%，魔防%+25.0%；出场盾+受击魔法盾；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>独立脚本（出场盾+受击魔法盾）</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>剑尊庇佑</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="n">
+      <c r="A58" s="7" t="n">
         <v>67130</v>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>兔击长空</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D58" s="8" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>物理攻击(暴击吸血)(0)；目标7；倍率[1200]；MP1；CD1</t>
         </is>
       </c>
-      <c r="E58" s="10" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>兔击长空</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="n">
+      <c r="A59" s="7" t="n">
         <v>67131</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>正义审判</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>脚本20023(1, 250, 0)；目标1；倍率[0]</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>精确（当前生命25%脚本）</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>正义审判</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="n">
+      <c r="A60" s="7" t="n">
         <v>67132</v>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>野蛮增长</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤3(每层15.0%，999回合)</t>
         </is>
       </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>野蛮增长</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="n">
+      <c r="A61" s="7" t="n">
         <v>67133</v>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>神兔庇佑</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>攻速%+15.0%，物攻%+15.0%，物防%+20.0%，魔防%+20.0%；首次受击增伤+免伤盾()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>独立脚本（首次受击+20%物伤；受击30%几率30%减伤3回合）</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>神兔觉醒</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="n">
+      <c r="A62" s="7" t="n">
         <v>67200</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>阴阳怒焱</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D62" s="8" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>随机阳/阴形态()；目标1；倍率[1800]</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>独立脚本（40%阳焱全体+灼烧5%；60%阴焱2目标×2+50%眩晕）</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>阴阳怒焱</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="n">
+      <c r="A63" s="7" t="n">
         <v>67207</v>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>麒麟庇护</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>暴击+20.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%；攻击清增益；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>独立脚本（30%几率清除目标1个增益）</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>麒麟庇护</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="n">
+      <c r="A64" s="7" t="n">
         <v>67300</v>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>麒麟浴火</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>叠层+伤害分担；目标1；倍率[1000]；CD1；buff:叠层增伤3(每层10.0%，999回合)</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>独立脚本（叠层增伤+55%几率35%伤害分担）</t>
         </is>
       </c>
-      <c r="F64" s="8" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>麒麟浴火</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="n">
+      <c r="A65" s="7" t="n">
         <v>67302</v>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>麒麟御风</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，2回合)</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>麒麟御风</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="n">
+      <c r="A66" s="7" t="n">
         <v>67304</v>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>花仙守护</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>被动触发；目标1；倍率[1000]；CD99；buff:复活(100.0%生命复活，999回合)</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
         <is>
           <t>花仙守护</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="n">
+      <c r="A67" s="7" t="n">
         <v>67305</v>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>百花盾</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>减伤/反伤/沉默；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr">
+      <c r="E67" s="8" t="inlineStr">
         <is>
           <t>独立脚本（减伤/反伤/沉默）</t>
         </is>
       </c>
-      <c r="F67" s="8" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>百花盾</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="n">
+      <c r="A68" s="7" t="n">
         <v>67306</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>仙泽福佑</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>死亡回全队血；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>独立脚本（死亡回全队40%生命）</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
+      <c r="F68" s="7" t="inlineStr">
         <is>
           <t>仙泽福佑</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="n">
+      <c r="A69" s="7" t="n">
         <v>67307</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>仙道神体</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>闪避+200，生命%+30.0%，物防%+25.0%，魔防%+25.0%；被动触发；目标1；倍率[1000]；CD99；buff:减伤(70.0%减伤，2回合)</t>
         </is>
       </c>
-      <c r="E69" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="inlineStr">
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>仙道神体</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="n">
+      <c r="A70" s="7" t="n">
         <v>67308</v>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>身外化身</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>被动触发；目标1；倍率[1000]；CD99；buff:复活(80.0%生命复活，999回合)</t>
         </is>
       </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
         <is>
           <t>身外化身</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="n">
+      <c r="A71" s="7" t="n">
         <v>67309</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>金箍棒头</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>物理攻击(暴击吸血)(0)；目标3×3；倍率[466, 466, 468]；3段</t>
         </is>
       </c>
-      <c r="E71" s="10" t="inlineStr">
+      <c r="E71" s="9" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
+      <c r="F71" s="7" t="inlineStr">
         <is>
           <t>金箍棒头</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="n">
+      <c r="A72" s="7" t="n">
         <v>67310</v>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>筋斗云决</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>速度条件增伤/减伤；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E72" s="9" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t>独立脚本（速度条件增伤/减伤）</t>
         </is>
       </c>
-      <c r="F72" s="8" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>筋斗云决</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="n">
+      <c r="A73" s="7" t="n">
         <v>67311</v>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>法天象地</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>暴击+10.0%，攻速%+15.0%，物攻%+15.0%，魔防%+25.0%</t>
         </is>
       </c>
-      <c r="E73" s="9" t="inlineStr">
+      <c r="E73" s="8" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr">
+      <c r="F73" s="7" t="inlineStr">
         <is>
           <t>法天象地</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="n">
+      <c r="A74" s="7" t="n">
         <v>67314</v>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>神隐</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>被动触发；目标1；倍率[1000]；CD99；buff:隐身(2回合)</t>
         </is>
       </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr">
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
         <is>
           <t>神隐</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="n">
+      <c r="A75" s="7" t="n">
         <v>67315</v>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>金刚之躯</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>魔法暴击+10.0%，攻速%+10.0%，魔攻%+15.0%，物防%+30.0%；被动触发；目标1；倍率[1000]；CD1；buff:减伤(20.0%减伤，2回合)</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>金刚之躯</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="n">
+      <c r="A76" s="7" t="n">
         <v>67316</v>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>三味真火</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>魔法攻击(0)；目标3×3；倍率[466, 466, 468]；3段</t>
         </is>
       </c>
-      <c r="E76" s="10" t="inlineStr">
+      <c r="E76" s="9" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
+      <c r="F76" s="7" t="inlineStr">
         <is>
           <t>三味真火</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="n">
+      <c r="A77" s="7" t="n">
         <v>67330</v>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>八方俱灭</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>物理攻击(暴击吸血)(500)；目标4×2；倍率[700, 700]；2段</t>
         </is>
       </c>
-      <c r="E77" s="10" t="inlineStr">
+      <c r="E77" s="9" t="inlineStr">
         <is>
           <t>近似（50%暴击吸血）</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>八方俱灭</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="n">
+      <c r="A78" s="7" t="n">
         <v>67331</v>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>死亡冲锋</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>周期攻速/物攻()；目标1；倍率[1000]；CD1；buff:攻速(攻速+20.0%，2回合)、物攻(物攻+30.0%，2回合)</t>
         </is>
       </c>
-      <c r="E78" s="9" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>独立脚本（每2回合攻速+20%/物攻+30%，持续2回合）</t>
         </is>
       </c>
-      <c r="F78" s="8" t="inlineStr">
+      <c r="F78" s="7" t="inlineStr">
         <is>
           <t>死亡冲锋</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="n">
+      <c r="A79" s="7" t="n">
         <v>67332</v>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>八方物连</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>连击(600, 0, 1350, 1350)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E79" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F79" s="8" t="inlineStr">
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>八方物连</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="n">
+      <c r="A80" s="7" t="n">
         <v>67333</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>战神圣体</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>暴击+10.0%，攻速%+15.0%，物攻%+18.0%，魔防%+25.0%；攻击为主人加怒；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E80" s="9" t="inlineStr">
+      <c r="E80" s="8" t="inlineStr">
         <is>
           <t>独立脚本（60%攻击为主人+5怒气；属性已生效）</t>
         </is>
       </c>
-      <c r="F80" s="8" t="inlineStr">
+      <c r="F80" s="7" t="inlineStr">
         <is>
           <t>战神圣体</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="n">
+      <c r="A81" s="7" t="n">
         <v>67334</v>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>神龙吐珠</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>魔法攻击(0)；目标4×2；倍率[700, 700]；2段；buff:法术吸血(10.0%吸血，1回合)</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr">
+      <c r="E81" s="9" t="inlineStr">
         <is>
           <t>近似（10%法术吸血）</t>
         </is>
       </c>
-      <c r="F81" s="8" t="inlineStr">
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>八方俱灭</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="n">
+      <c r="A82" s="7" t="n">
         <v>67335</v>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="7" t="inlineStr">
         <is>
           <t>死亡追击</t>
         </is>
       </c>
-      <c r="C82" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>击杀法术追击()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E82" s="9" t="inlineStr">
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>独立脚本（法术技能击杀后追击一次技能）</t>
         </is>
       </c>
-      <c r="F82" s="8" t="inlineStr">
+      <c r="F82" s="7" t="inlineStr">
         <is>
           <t>死亡追击</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="n">
+      <c r="A83" s="7" t="n">
         <v>67336</v>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="7" t="inlineStr">
         <is>
           <t>龙盾</t>
         </is>
       </c>
-      <c r="C83" s="8" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限100.0%，1回合)</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F83" s="8" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
         <is>
           <t>龙盾</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="n">
+      <c r="A84" s="7" t="n">
         <v>67337</v>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>龙尊道体</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>魔法暴击+15.0%，攻速%+12.0%，魔攻%+15.0%，物防%+25.0%；被动触发；目标1；倍率[1000]；CD1；buff:伤害免疫(50.0%免疫，1回合)</t>
         </is>
       </c>
-      <c r="E84" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="inlineStr">
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>龙尊道体</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="n">
+      <c r="A85" s="7" t="n">
         <v>67338</v>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>玄女功</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>物理攻击(暴击吸血)(0)；目标3/4/5；倍率[466, 466, 468]；3段</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr">
+      <c r="E85" s="9" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
       </c>
-      <c r="F85" s="8" t="inlineStr">
+      <c r="F85" s="7" t="inlineStr">
         <is>
           <t>玄女功</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="n">
+      <c r="A86" s="7" t="n">
         <v>67339</v>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>天地双连</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>连击(700, 0, 1200, 1200)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E86" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F86" s="8" t="inlineStr">
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
         <is>
           <t>天地双连</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="n">
+      <c r="A87" s="7" t="n">
         <v>67340</v>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>玄天暴</t>
         </is>
       </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>随机双倍/三倍+速度增伤；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E87" s="9" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>独立脚本（随机双/三倍+速度增伤）</t>
         </is>
       </c>
-      <c r="F87" s="8" t="inlineStr">
+      <c r="F87" s="7" t="inlineStr">
         <is>
           <t>玄天暴</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="n">
+      <c r="A88" s="7" t="n">
         <v>67341</v>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>玄天盾</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限100.0%，1回合)、伤害免疫(10.0%免疫，999回合)</t>
         </is>
       </c>
-      <c r="E88" s="10" t="inlineStr">
+      <c r="E88" s="9" t="inlineStr">
         <is>
           <t>近似（护盾+10%免疫）</t>
         </is>
       </c>
-      <c r="F88" s="8" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>玄天盾</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="n">
+      <c r="A89" s="7" t="n">
         <v>67342</v>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>玄女圣体</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>暴击+15.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%；攻击不加怒/扣目标怒；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E89" s="9" t="inlineStr">
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t>独立脚本（攻击不涨怒并扣第一目标5怒；属性已生效）</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr">
+      <c r="F89" s="7" t="inlineStr">
         <is>
           <t>玄女圣体</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="n">
+      <c r="A90" s="7" t="n">
         <v>67343</v>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>初音飓风</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D90" s="8" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>魔法攻击(0)；目标3/3/6；倍率[466, 466, 468]；3段</t>
         </is>
       </c>
-      <c r="E90" s="10" t="inlineStr">
+      <c r="E90" s="9" t="inlineStr">
         <is>
           <t>近似（倍率推断）</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr">
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>初音风暴</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="n">
+      <c r="A91" s="7" t="n">
         <v>67344</v>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>乘风</t>
         </is>
       </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D91" s="8" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤99(每层10.0%，999回合)</t>
         </is>
       </c>
-      <c r="E91" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F91" s="8" t="inlineStr">
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
         <is>
           <t>乘风</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="n">
+      <c r="A92" s="7" t="n">
         <v>67345</v>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>天佑</t>
         </is>
       </c>
-      <c r="C92" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D92" s="8" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>复活+伤害分担；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E92" s="9" t="inlineStr">
+      <c r="E92" s="8" t="inlineStr">
         <is>
           <t>独立脚本（首次死亡50%复活；每回合40%几率35%伤害分担2回合）</t>
         </is>
       </c>
-      <c r="F92" s="8" t="inlineStr">
+      <c r="F92" s="7" t="inlineStr">
         <is>
           <t>天佑</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="n">
+      <c r="A93" s="7" t="n">
         <v>67346</v>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>风盾</t>
         </is>
       </c>
-      <c r="C93" s="8" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，1回合)</t>
         </is>
       </c>
-      <c r="E93" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F93" s="8" t="inlineStr">
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>风盾</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="n">
+      <c r="A94" s="7" t="n">
         <v>67347</v>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>初音圣体</t>
         </is>
       </c>
-      <c r="C94" s="8" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>魔法暴击+20.0%，攻速%+18.0%，魔攻%+15.0%，物防%+25.0%；初音圣体（阈值减伤）()；目标1；倍率[1000]；CD2</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（单次伤害&gt;50%生命时80%几率降至40%，+20%伤害2回合，CD3；覆盖普通/反击/协助伤害）</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>初音圣体</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n">
+        <v>67348</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>穷凶烈爪</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>主动</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>物理攻击(暴击吸血)(0)；目标2/3；倍率[700, 700]；2段</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>近似（倍率推断）</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>穷凶烈爪</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="n">
+        <v>67349</v>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>列字秘</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>物攻%+5.0%，魔攻%+3.0%；连击(1000, 0, 1000, 1000)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>九秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n">
+        <v>67352</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>穷奇圣体</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>暴击+5.0%，攻速%+10.0%，物攻%+10.0%；物穿(100)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>穷奇圣体</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n">
+        <v>67353</v>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>封阳击</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>主动</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>物穿(0)；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（5–8段随机；击杀后自动转火）</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>封阳击</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n">
+        <v>67354</v>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>突袭</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>物穿(280)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>突袭</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="n">
+        <v>67355</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>禁魂</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>禁魂(200, 200)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>禁魂</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="n">
+        <v>67356</v>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>封盾</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>护盾</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，1回合)</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>封盾</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="n">
+        <v>67357</v>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>封阳圣体</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>暴击+20.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%；物穿(350)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>封阳圣体</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="n">
+        <v>67358</v>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>太初决</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>主动</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>魔法攻击(0)；目标3/4/10；倍率[466, 466, 468]；3段</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>近似（倍率推断）</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>太初决</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="n">
+        <v>67359</v>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>破竹</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>法术吸血+受击减伤；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（25%法术吸血+受击减伤）</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>破竹</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="n">
+        <v>67360</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>扶摇</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤99(每层15.0%，999回合)</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>扶摇</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="n">
+        <v>67361</v>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>搬山</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>护盾</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>搬山护盾/增伤/复活()；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（前3回合魔伤+40%/攻速+30%；出场200%护盾1回合；首次死亡60%复活）</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>搬山</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="n">
+        <v>67362</v>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>太初圣体</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；法穿(300)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>太初圣体</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="n">
+        <v>67363</v>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>死亡镰刀</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>主动</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>魔法攻击(0)；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（5–8段随机；击杀后自动转火；每段20%眩晕2回合）</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>死亡镰刀</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="n">
+        <v>67364</v>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>破道</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>法穿(300)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>破道</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="n">
+        <v>67365</v>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>转阳</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>击杀回血+燃火；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（击杀回血+燃火增伤）</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>转阳</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="n">
+        <v>67366</v>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>死神盾</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>护盾</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>被动触发；目标1；倍率[1000]；CD99；buff:次数护盾(挡6次，1回合)</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>死神盾</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n">
+        <v>67367</v>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>死神神体</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；无视防御+阵亡增伤()；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（攻击人物无视30%防；每个阵亡友方+10%伤害/+20%魔防）</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>死神神体</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="n">
+        <v>67368</v>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>无忧击</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>主动</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>附加治疗/护盾()；目标4×3；倍率[466, 466, 468]；3段</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（每段附加治疗+20%护盾近似）</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>无忧击</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n">
+        <v>67369</v>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>化魂</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>被动触发；目标1；倍率[1000]；CD99；buff:复活(150.0%生命复活，999回合)</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>化魂</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="n">
+        <v>67370</v>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>叠法</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>连击(300, 0, 700, 700)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>叠法</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n">
+        <v>67371</v>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>亡川盾</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>护盾</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>被动触发；目标1；倍率[1000]；CD99；buff:次数护盾(挡6次，1回合)</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>亡川盾</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="n">
+        <v>67372</v>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>亡川神体</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>暴击+20.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%；物穿(350)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>亡川神体</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n">
+        <v>67378</v>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>乾坤天降</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>主动</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>乾坤天降（风雷）()；目标6；倍率[1200]</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（主目标+相邻5目标同倍率；释放后+15%物攻/速度/生命；风雷护盾30%几率250%生命2回合，几率推断）</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>乾坤·天降</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="n">
+        <v>67379</v>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>九龙神火</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>连击(400, 0, 1800, 1800)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>近似（触发脚本）</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>九龙神火</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n">
+        <v>67503</v>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>者字秘</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D94" s="8" t="inlineStr">
-        <is>
-          <t>魔法暴击+20.0%，攻速%+18.0%，魔攻%+15.0%，物防%+25.0%</t>
-        </is>
-      </c>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（需受击前伤害值；引擎无该hook，未做）</t>
-        </is>
-      </c>
-      <c r="F94" s="8" t="inlineStr">
-        <is>
-          <t>初音圣体</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="8" t="n">
-        <v>67348</v>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>穷凶烈爪</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="inlineStr">
-        <is>
-          <t>主动</t>
-        </is>
-      </c>
-      <c r="D95" s="8" t="inlineStr">
-        <is>
-          <t>物理攻击(暴击吸血)(0)；目标2/3；倍率[700, 700]；2段</t>
-        </is>
-      </c>
-      <c r="E95" s="10" t="inlineStr">
-        <is>
-          <t>近似（倍率推断）</t>
-        </is>
-      </c>
-      <c r="F95" s="8" t="inlineStr">
-        <is>
-          <t>穷凶烈爪</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="8" t="n">
-        <v>67349</v>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>列字秘</t>
-        </is>
-      </c>
-      <c r="C96" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t>物攻%+5.0%，魔攻%+3.0%；连击(1000, 0, 1000, 1000)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E96" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F96" s="8" t="inlineStr">
-        <is>
-          <t>九秘</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="8" t="n">
-        <v>67352</v>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>穷奇圣体</t>
-        </is>
-      </c>
-      <c r="C97" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t>暴击+5.0%，攻速%+10.0%，物攻%+10.0%；物穿(100)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E97" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F97" s="8" t="inlineStr">
-        <is>
-          <t>穷奇圣体</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="8" t="n">
-        <v>67353</v>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>封阳击</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="inlineStr">
-        <is>
-          <t>主动</t>
-        </is>
-      </c>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>物穿(0)；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>独立脚本（5–8段随机；击杀后自动转火）</t>
-        </is>
-      </c>
-      <c r="F98" s="8" t="inlineStr">
-        <is>
-          <t>封阳击</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="8" t="n">
-        <v>67354</v>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>突袭</t>
-        </is>
-      </c>
-      <c r="C99" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t>物穿(280)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E99" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t>突袭</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="8" t="n">
-        <v>67355</v>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>禁魂</t>
-        </is>
-      </c>
-      <c r="C100" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t>禁魂(200, 200)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E100" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F100" s="8" t="inlineStr">
-        <is>
-          <t>禁魂</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="8" t="n">
-        <v>67356</v>
-      </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>封盾</t>
-        </is>
-      </c>
-      <c r="C101" s="8" t="inlineStr">
-        <is>
-          <t>护盾</t>
-        </is>
-      </c>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，1回合)</t>
-        </is>
-      </c>
-      <c r="E101" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F101" s="8" t="inlineStr">
-        <is>
-          <t>封盾</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="8" t="n">
-        <v>67357</v>
-      </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>封阳圣体</t>
-        </is>
-      </c>
-      <c r="C102" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t>暴击+20.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%；物穿(350)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E102" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>封阳圣体</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="8" t="n">
-        <v>67358</v>
-      </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>太初决</t>
-        </is>
-      </c>
-      <c r="C103" s="8" t="inlineStr">
-        <is>
-          <t>主动</t>
-        </is>
-      </c>
-      <c r="D103" s="8" t="inlineStr">
-        <is>
-          <t>魔法攻击(0)；目标3/4/10；倍率[466, 466, 468]；3段</t>
-        </is>
-      </c>
-      <c r="E103" s="10" t="inlineStr">
-        <is>
-          <t>近似（倍率推断）</t>
-        </is>
-      </c>
-      <c r="F103" s="8" t="inlineStr">
-        <is>
-          <t>太初决</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="8" t="n">
-        <v>67359</v>
-      </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>破竹</t>
-        </is>
-      </c>
-      <c r="C104" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D104" s="8" t="inlineStr">
-        <is>
-          <t>法术吸血+受击减伤；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>独立脚本（25%法术吸血+受击减伤）</t>
-        </is>
-      </c>
-      <c r="F104" s="8" t="inlineStr">
-        <is>
-          <t>破竹</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="8" t="n">
-        <v>67360</v>
-      </c>
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>扶摇</t>
-        </is>
-      </c>
-      <c r="C105" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D105" s="8" t="inlineStr">
-        <is>
-          <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤99(每层15.0%，999回合)</t>
-        </is>
-      </c>
-      <c r="E105" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F105" s="8" t="inlineStr">
-        <is>
-          <t>扶摇</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="8" t="n">
-        <v>67361</v>
-      </c>
-      <c r="B106" s="8" t="inlineStr">
-        <is>
-          <t>搬山</t>
-        </is>
-      </c>
-      <c r="C106" s="8" t="inlineStr">
-        <is>
-          <t>护盾</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="inlineStr">
-        <is>
-          <t>搬山护盾/增伤/复活()；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E106" s="9" t="inlineStr">
-        <is>
-          <t>独立脚本（前3回合魔伤+40%/攻速+30%；出场200%护盾1回合；首次死亡60%复活）</t>
-        </is>
-      </c>
-      <c r="F106" s="8" t="inlineStr">
-        <is>
-          <t>搬山</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="8" t="n">
-        <v>67362</v>
-      </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>太初圣体</t>
-        </is>
-      </c>
-      <c r="C107" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D107" s="8" t="inlineStr">
-        <is>
-          <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；法穿(300)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E107" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F107" s="8" t="inlineStr">
-        <is>
-          <t>太初圣体</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="8" t="n">
-        <v>67363</v>
-      </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>死亡镰刀</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="inlineStr">
-        <is>
-          <t>主动</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="inlineStr">
-        <is>
-          <t>魔法攻击(0)；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
-        </is>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
-        <is>
-          <t>独立脚本（5–8段随机；击杀后自动转火；每段20%眩晕2回合）</t>
-        </is>
-      </c>
-      <c r="F108" s="8" t="inlineStr">
-        <is>
-          <t>死亡镰刀</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="8" t="n">
-        <v>67364</v>
-      </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>破道</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D109" s="8" t="inlineStr">
-        <is>
-          <t>法穿(300)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E109" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F109" s="8" t="inlineStr">
-        <is>
-          <t>破道</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="8" t="n">
-        <v>67365</v>
-      </c>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>转阳</t>
-        </is>
-      </c>
-      <c r="C110" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D110" s="8" t="inlineStr">
-        <is>
-          <t>击杀回血+燃火；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E110" s="9" t="inlineStr">
-        <is>
-          <t>独立脚本（击杀回血+燃火增伤）</t>
-        </is>
-      </c>
-      <c r="F110" s="8" t="inlineStr">
-        <is>
-          <t>转阳</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="8" t="n">
-        <v>67366</v>
-      </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>死神盾</t>
-        </is>
-      </c>
-      <c r="C111" s="8" t="inlineStr">
-        <is>
-          <t>护盾</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="inlineStr">
-        <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:次数护盾(挡6次，1回合)</t>
-        </is>
-      </c>
-      <c r="E111" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F111" s="8" t="inlineStr">
-        <is>
-          <t>死神盾</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="8" t="n">
-        <v>67367</v>
-      </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>死神神体</t>
-        </is>
-      </c>
-      <c r="C112" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D112" s="8" t="inlineStr">
-        <is>
-          <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；无视防御+阵亡增伤()；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E112" s="9" t="inlineStr">
-        <is>
-          <t>独立脚本（攻击人物无视30%防；每个阵亡友方+10%伤害/+20%魔防）</t>
-        </is>
-      </c>
-      <c r="F112" s="8" t="inlineStr">
-        <is>
-          <t>死神神体</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="8" t="n">
-        <v>67368</v>
-      </c>
-      <c r="B113" s="8" t="inlineStr">
-        <is>
-          <t>无忧击</t>
-        </is>
-      </c>
-      <c r="C113" s="8" t="inlineStr">
-        <is>
-          <t>主动</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="inlineStr">
-        <is>
-          <t>附加治疗/护盾()；目标4×3；倍率[466, 466, 468]；3段</t>
-        </is>
-      </c>
-      <c r="E113" s="9" t="inlineStr">
-        <is>
-          <t>独立脚本（每段附加治疗+20%护盾近似）</t>
-        </is>
-      </c>
-      <c r="F113" s="8" t="inlineStr">
-        <is>
-          <t>无忧击</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="8" t="n">
-        <v>67369</v>
-      </c>
-      <c r="B114" s="8" t="inlineStr">
-        <is>
-          <t>化魂</t>
-        </is>
-      </c>
-      <c r="C114" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D114" s="8" t="inlineStr">
-        <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:复活(150.0%生命复活，999回合)</t>
-        </is>
-      </c>
-      <c r="E114" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F114" s="8" t="inlineStr">
-        <is>
-          <t>化魂</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="8" t="n">
-        <v>67370</v>
-      </c>
-      <c r="B115" s="8" t="inlineStr">
-        <is>
-          <t>叠法</t>
-        </is>
-      </c>
-      <c r="C115" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="inlineStr">
-        <is>
-          <t>连击(300, 0, 700, 700)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E115" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F115" s="8" t="inlineStr">
-        <is>
-          <t>叠法</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="8" t="n">
-        <v>67371</v>
-      </c>
-      <c r="B116" s="8" t="inlineStr">
-        <is>
-          <t>亡川盾</t>
-        </is>
-      </c>
-      <c r="C116" s="8" t="inlineStr">
-        <is>
-          <t>护盾</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="inlineStr">
-        <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:次数护盾(挡6次，1回合)</t>
-        </is>
-      </c>
-      <c r="E116" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F116" s="8" t="inlineStr">
-        <is>
-          <t>亡川盾</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="8" t="n">
-        <v>67372</v>
-      </c>
-      <c r="B117" s="8" t="inlineStr">
-        <is>
-          <t>亡川神体</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D117" s="8" t="inlineStr">
-        <is>
-          <t>暴击+20.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%；物穿(350)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E117" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F117" s="8" t="inlineStr">
-        <is>
-          <t>亡川神体</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="8" t="n">
-        <v>67378</v>
-      </c>
-      <c r="B118" s="8" t="inlineStr">
-        <is>
-          <t>乾坤天降</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t>主动</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="inlineStr">
-        <is>
-          <t>物理攻击(暴击吸血)(0)；目标6；倍率[1200]</t>
-        </is>
-      </c>
-      <c r="E118" s="11" t="inlineStr">
-        <is>
-          <t>部分（主目标+相邻5目标同倍率；风雷护盾触发未做；15%速度加成未落表）</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="inlineStr">
-        <is>
-          <t>乾坤·天降</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="8" t="n">
-        <v>67379</v>
-      </c>
-      <c r="B119" s="8" t="inlineStr">
-        <is>
-          <t>九龙神火</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="inlineStr">
-        <is>
-          <t>连击(400, 0, 1800, 1800)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E119" s="10" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F119" s="8" t="inlineStr">
-        <is>
-          <t>九龙神火</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="8" t="n">
-        <v>67503</v>
-      </c>
-      <c r="B120" s="8" t="inlineStr">
-        <is>
-          <t>者字秘</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t>被动</t>
-        </is>
-      </c>
-      <c r="D120" s="8" t="inlineStr">
+      <c r="D120" s="7" t="inlineStr">
         <is>
           <t>生命=等级×80.0+1000</t>
         </is>
       </c>
-      <c r="E120" s="9" t="inlineStr">
+      <c r="E120" s="8" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F120" s="8" t="inlineStr">
+      <c r="F120" s="7" t="inlineStr">
         <is>
           <t>九秘</t>
         </is>
@@ -4274,7 +4245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4286,99 +4257,39 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>当前效果</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>技能说明</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="n">
-        <v>67347</v>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>初音圣体</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>被动</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>魔法暴击+20.0%，攻速%+18.0%，魔攻%+15.0%，物防%+25.0%</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>仅属性（需受击前伤害值；引擎无该hook，未做）</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>初音圣体</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="n">
-        <v>67378</v>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>乾坤天降</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>主动</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>物理攻击(暴击吸血)(0)；目标6；倍率[1200]</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>部分（主目标+相邻5目标同倍率；风雷护盾触发未做；15%速度加成未落表）</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>乾坤·天降</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F3"/>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>魔攻%+20.0%；魔法攻击(0)；目标4；倍率[1800]</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>近似（倍率推断）</t>
+          <t>魔攻%+20.0%；灵魂超度（条件倍率）()；目标4；倍率[1800]</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（&lt;50%生命2倍，否则150%；+20%魔攻）</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>物穿(0)；目标1×2；倍率[700, 700]；2段</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>近似（倍率推断）</t>
+          <t>枭刃（1-2段）()；目标1；倍率[700, 700]</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（1–2段随机；倍率推断）</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>物理攻击(暴击吸血)(0)；目标7；倍率[1200]；MP1；CD1</t>
-        </is>
-      </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>近似（倍率推断）</t>
+          <t>兔击长空()；目标7；倍率[1200]；MP1；CD1</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（7目标物理；降速几率未做）</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>物理攻击(暴击吸血)(0)；目标3×3；倍率[466, 466, 468]；3段</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>近似（倍率推断）</t>
+          <t>金箍棒头()；目标3×3；倍率[466, 466, 468]；3段</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（3×3物理；金刚/怒目几率未做）</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -2899,12 +2899,12 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>魔法攻击(0)；目标3×3；倍率[466, 466, 468]；3段</t>
-        </is>
-      </c>
-      <c r="E76" s="9" t="inlineStr">
-        <is>
-          <t>近似（倍率推断）</t>
+          <t>三味真火()；目标3×3；倍率[466, 466, 468]；3段</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（3×3魔法；天残/迟暮几率未做）</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>物理攻击(暴击吸血)(0)；目标3/4/5；倍率[466, 466, 468]；3段</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>近似（倍率推断）</t>
+          <t>玄女功()；目标3/4/5；倍率[466, 466, 468]；3段</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（3/4/5目标物理）</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>魔法攻击(0)；目标3/3/6；倍率[466, 466, 468]；3段</t>
-        </is>
-      </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>近似（倍率推断）</t>
+          <t>初音飓风+驱散()；目标3/3/6；倍率[466, 466, 468]；3段</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（3/3/6魔法+必定驱散）</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>物理攻击(暴击吸血)(0)；目标2/3；倍率[700, 700]；2段</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>近似（倍率推断）</t>
+          <t>穷凶烈爪+暴击吸血()；目标2/3；倍率[700, 700]；2段</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（2/3目标物理；主目标暴击吸血30%；护盾几率未做）</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>物穿(0)；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
+          <t>封阳击（独立物理）()；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>独立脚本（5–8段随机；击杀后自动转火）</t>
+          <t>独立脚本（5–8段随机；击杀后自动转火；物理攻击脚本已修正）</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>魔法攻击(0)；目标3/4/10；倍率[466, 466, 468]；3段</t>
-        </is>
-      </c>
-      <c r="E103" s="9" t="inlineStr">
-        <is>
-          <t>近似（倍率推断）</t>
+          <t>太初决+驱散()；目标3/4/10；倍率[466, 466, 468]；3段；buff:小萌羊(3回合)、小萌羊(3回合)、小萌羊(3回合)</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（3/4/10魔法+必定驱散；20%小萌羊3回合）</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>独立脚本（主目标+相邻5目标同倍率；释放后+15%物攻/速度/生命；风雷护盾30%几率250%生命2回合，几率推断）</t>
+          <t>独立脚本（主目标+相邻5目标同倍率；释放后+15%物攻/速度/生命；风雷护盾70%几率250%生命2回合）</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">

--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>治疗(80, 200)；目标3；倍率[1000]；buff:持续回血(每回合5.0%，3回合)</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>近似（治疗/护盾参数）</t>
+          <t>推气过穴（独立治疗）(80, 200)；目标3；倍率[1000]；buff:持续回血(每回合5.0%，3回合)</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（3人，立即8%+200，每回合5%回血3回合）</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>治疗(120, 200)；目标4；倍率[1000]；buff:持续回血(每回合8.0%，3回合)</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>近似（治疗/护盾参数）</t>
+          <t>生命化泉（独立治疗）(120, 200)；目标4；倍率[1000]；buff:持续回血(每回合8.0%，3回合)</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（4人，立即12%+200，每回合8%回血3回合）</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>回蓝(300, 0)；目标5；倍率[1000]；MP3</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>近似（治疗/护盾参数）</t>
+          <t>炼气化神（独立回蓝）(300, 0)；目标5；倍率[1000]；MP3；CD3</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（5人，回复30%最大魔法，CD3）</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2239,12 +2239,12 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>纯 buff；目标13；倍率[1000]；MP4；CD2；buff:减伤(50.0%减伤，3回合)</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>近似（治疗/护盾参数）</t>
+          <t>罗汉金钟（独立魔法盾）()；目标13；倍率[1000]；MP4；CD2</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（全体，魔法减伤50%3回合，CD2）</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>纯 buff；目标1；倍率[1000]；buff:反伤(35.0%反伤，3回合)</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>近似（治疗/护盾参数）</t>
+          <t>菩提明镜（独立反伤盾）()；目标1；倍率[1000]；buff:反伤(35.0%反伤，3回合)</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（1人，反伤35%3回合）</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>独立脚本（7目标物理；降速几率未做）</t>
+          <t>独立脚本（7目标物理；降速有几率暂按70%记录）</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>独立脚本（3×3物理；金刚/怒目几率未做）</t>
+          <t>独立脚本（3×3物理；金刚/怒目有几率暂按70%记录）</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>独立脚本（3×3魔法；天残/迟暮几率未做）</t>
+          <t>独立脚本（3×3魔法；天残/迟暮有几率暂按70%记录）</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>独立脚本（2/3目标物理；主目标暴击吸血30%；护盾几率未做）</t>
+          <t>独立脚本（2/3目标物理；主目标暴击吸血30%；护盾有几率暂按70%记录）</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">

--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -56,12 +56,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,10 +104,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -526,25 +526,25 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>近似</t>
+          <t>独立脚本</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>独立脚本</t>
+          <t>近似</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>精确</t>
         </is>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>魔法攻击(0)；目标3；倍率[1600]；MP99；buff:生命护盾(生命上限200.0%，2回合)、封心(封心50.0%，2回合)</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>近似（封心+护盾已接）</t>
+          <t>郎神共舞（独立）()；目标3；倍率[1600]；MP99</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（3目标魔法；50%主目标封心；70%一次免伤）</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>物理攻击(暴击吸血)(200)；目标4；倍率[1800]</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>近似（20%暴击吸血）</t>
+          <t>天诛（独立）()；目标4；倍率[1800]</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（4目标物理；暴击吸血20%）</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>纯 buff；目标13；倍率[1000]；MP4；CD2；buff:增伤(20.0%增伤，3回合)</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>近似（群增伤20%）</t>
+          <t>燃烧之光（独立）()；目标13；倍率[1000]；MP4；CD2；buff:增伤(20.0%增伤，3回合)</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（全队+20%伤害3回合，CD2）</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>物理攻击(暴击吸血)(500)；目标4×2；倍率[700, 700]；2段</t>
-        </is>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>近似（50%暴击吸血）</t>
+          <t>八方俱灭（独立）()；目标4×2；倍率[700, 700]；2段</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（2×4物理；主目标暴击吸血50%）</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>魔法攻击(0)；目标4×2；倍率[700, 700]；2段；buff:法术吸血(10.0%吸血，1回合)</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>近似（10%法术吸血）</t>
+          <t>神龙吐珠（独立）()；目标4×2；倍率[700, 700]；2段；buff:法术吸血(10.0%吸血，1回合)</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（2×4魔法；10%法术吸血）</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限100.0%，1回合)、伤害免疫(10.0%免疫，999回合)</t>
-        </is>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>近似（护盾+10%免疫）</t>
+          <t>玄天盾（独立）；目标1；倍率[1000]；CD0</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（出场/召唤100%盾1回合；10%致命免疫）</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">

--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -799,12 +799,12 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>脚本32001(400, 350, 0, 75)；目标1；倍率[1000]；CD4</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>超级涅槃（独立）(400, 350, 0, 75)；目标1；倍率[1000]；CD4</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（主人死亡40%复活35%生命，上限等级×75）</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>神佑(140, 180, 220, 280, 1000, 0)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>超级神佑（独立）(140, 180, 220, 280, 1000, 0)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（死亡28%复活100%生命，体质修正）</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>逃生(490, 0, 150)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>超级逃生（独立）(490, 0, 150)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（致命伤害49%回复150）</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，2回合)、反伤(20.0%反伤，999回合)</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>换天之术（独立）；目标1；倍率[1000]；CD99</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（出场200%盾2回合+20%反伤；首次死亡复活20%）</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:复活(100.0%生命复活，999回合)</t>
-        </is>
-      </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>花仙守护（独立）；目标1；倍率[1000]；CD99；buff:魔防(3回合)</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（首次死亡100%复活100%生命，+30%魔防3回合）</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>魔法暴击+15.0%，攻速%+12.0%，魔攻%+15.0%，物防%+25.0%；被动触发；目标1；倍率[1000]；CD1；buff:伤害免疫(50.0%免疫，1回合)</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>魔法暴击+15.0%，攻速%+12.0%，魔攻%+15.0%，物防%+25.0%；龙尊道体（独立）；目标1；倍率[1000]；CD1</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（致命伤害50%免疫每回合一次；带60352/60353时80%）</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">

--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -919,12 +919,12 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>反弹(350, 650)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>超级反弹（独立）(350, 650)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（35%反弹65%）</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>还击(580, [60011, 60012, 60013)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>超级魔法还击（独立）(580, [60011, 60012, 60013)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（58%魔法还击）</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>生命%+5.0%，魔攻%+3.0%；法术连击；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>生命%+5.0%，魔攻%+3.0%；斗字秘（独立）；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（40%追加130%魔法攻击）</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>攻速%+20.0%；眩晕(800, 800, 800, 800)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>攻速%+20.0%；灵魂冲击（独立）(700, 700, 700, 700)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（70%眩晕1回合）</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>连击(500, 0, 1800, 1800)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>神兵加持（独立重放）()；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（50%重放天诛）</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>连击(600, 0, 1350, 1350)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>八方物连（独立）(600, 0, 1350, 1350)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（60%物理连击，倍率沿用135%）</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>连击(700, 0, 1200, 1200)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E86" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>天地双连（独立）(700, 0, 1200, 1200)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（70%物理连击120%）</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>物攻%+5.0%，魔攻%+3.0%；连击(1000, 0, 1000, 1000)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>物攻%+5.0%，魔攻%+3.0%；列字秘（独立追击）()；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（技能击杀追击最多2次；+5%物攻/+3%魔攻）</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>连击(300, 0, 700, 700)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E115" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>叠法（独立重放）()；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（30%重放无忧击70%伤害）</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>连击(400, 0, 1800, 1800)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E119" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>伤害加成+30.0%，攻速%+30.0%，魔防%+30.0%；九龙神火（独立重放）()；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（释放乾坤天降40%额外释放；+30%伤害/攻速/魔防）</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">

--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>审判(350)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>超级审判（独立）(350)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（对神佑/逃生目标+35%，击杀禁神佑）</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>驱鬼(1000, 80)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>超级驱鬼（独立）(1000, 80)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（鬼魂2倍伤害，无视8%物防）</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1279,12 +1279,12 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>物穿(400)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>兵字秘（独立）(400)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（物穿40%）</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>吸血(1000, 150)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>法术吸血（独立）(1000, 150)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（法术吸血15%）</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>禁魂(1000, 1000)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>魔气入体（独立）(1000, 1000)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（必定魔气入体3回合）</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>暴击+5.0%，攻速%+10.0%，物攻%+10.0%；物穿(100)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>暴击+5.0%，攻速%+10.0%，物攻%+10.0%；穷奇圣体（独立）()；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（攻击人物无视10%物魔防）</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>物穿(280)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>突袭（独立）(280)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（物穿28%）</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>禁魂(200, 200)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>禁魂（独立）(200, 200)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（20%禁魂5回合）</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
@@ -3679,12 +3679,12 @@
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>暴击+20.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%；物穿(350)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>暴击+20.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%；封阳圣体（独立）()；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（攻击人物无视35%物魔防）</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；法穿(300)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E107" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；太初圣体（独立）()；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（攻击人物无视30%物魔防）</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>法穿(300)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E109" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>破道（独立）(300)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（法穿30%）</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>暴击+20.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%；物穿(350)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E117" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>暴击+20.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%；亡川神体（独立）()；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（攻击人物无视35%物魔防）</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">

--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>生命%+35.0%，攻速%+18.0%，物防%+30.0%，魔防%+30.0%；被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，2回合)</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>生命%+35.0%，攻速%+18.0%，物防%+30.0%，魔防%+30.0%；白灵祝福（独立护盾）；目标1；倍率[1000]；CD99</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（出场200%盾2回合；属性已生效）</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，2回合)、反伤(20.0%反伤，999回合)</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>神猿加持（独立护盾）；目标1；倍率[1000]；CD99</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（出场200%盾2回合+20%反伤2回合）</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，2回合)</t>
-        </is>
-      </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>麒麟御风（独立护盾）；目标1；倍率[1000]；CD99</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（出场200%盾2回合；低血狂暴未做）</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>闪避+200，生命%+30.0%，物防%+25.0%，魔防%+25.0%；被动触发；目标1；倍率[1000]；CD99；buff:减伤(70.0%减伤，2回合)</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>闪避+200，生命%+30.0%，物防%+25.0%，魔防%+25.0%；仙道神体（独立减伤盾）；目标1；倍率[1000]；CD4</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（初始70%减伤盾2回合，CD5）</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限100.0%，1回合)</t>
-        </is>
-      </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>龙盾（独立护盾）；目标1；倍率[1000]；CD99</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（出场100%盾1回合；低血狂暴未做）</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
@@ -3409,12 +3409,12 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，1回合)</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>风盾（独立护盾）；目标1；倍率[1000]；CD99</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（前2回合+20%伤害/攻速；出场200%盾1回合）</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:生命护盾(生命上限200.0%，1回合)</t>
-        </is>
-      </c>
-      <c r="E101" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>封盾（独立护盾）；目标1；倍率[1000]；CD99</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（前3回合+30%伤害/40%攻速；出场200%盾1回合）</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:次数护盾(挡6次，1回合)</t>
-        </is>
-      </c>
-      <c r="E111" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>死神盾（独立护盾）；目标1；倍率[1000]；CD99</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（前3回合+30%伤害/40%攻速；出场挡6次盾1回合）</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:次数护盾(挡6次，1回合)</t>
-        </is>
-      </c>
-      <c r="E116" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>亡川盾（独立护盾）；目标1；倍率[1000]；CD99</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（前3回合+30%伤害/30%攻速；出场挡6次盾1回合）</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">

--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -530,27 +530,27 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>精确</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>近似</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>精确</t>
-        </is>
-      </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -979,12 +979,12 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>物理攻击(500, 300, 100)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>超级报复（独立）(500, 300, 100)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（低血增伤，阈值沿用10/30/50%）</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>脚本31000(380)；目标1；倍率[1000]；buff:物攻祝福(2回合)</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>超级物攻祝福（独立）(380)；目标1；倍率[1000]；buff:物攻祝福(2回合)</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（回合初38%概率+10%物攻2回合）</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>逆击(330)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>超级逆击（独立）(330)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（对祝福目标+33%）</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1249,12 +1249,12 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>命中+140；强击(150, 1700, 650)；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>命中+140；超级强击（独立）(150, 1700, 650)；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（对宠物+15%，目标生命&gt;1.7倍再+65%）</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>暴伤+20.0%；法术连击；目标1；倍率[1000]</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>暴伤+20.0%；神威（独立）；目标1；倍率[1000]</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（80%魔法连击；神威状态/暴伤未做）</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:隐身(2回合)</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>神隐（独立）；目标1；倍率[1000]；CD0</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（出场/召唤隐身2回合可攻击）</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>魔法暴击+10.0%，攻速%+10.0%，魔攻%+15.0%，物防%+30.0%；被动触发；目标1；倍率[1000]；CD1；buff:减伤(20.0%减伤，2回合)</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>魔法暴击+10.0%，攻速%+10.0%，魔攻%+15.0%，物防%+30.0%；金刚之躯（独立）；目标1；倍率[1000]；CD0</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（受击70%概率20%减伤2回合）</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤99(每层10.0%，999回合)</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>乘风（独立）；目标1；倍率[1000]；CD0；buff:叠层增伤99(每层10.0%，999回合)</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（每回合+10%魔攻叠层）</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤99(每层15.0%，999回合)</t>
-        </is>
-      </c>
-      <c r="E105" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>扶摇（独立）；目标1；倍率[1000]；CD0；buff:叠层增伤99(每层15.0%，999回合)</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（每回合+15%魔攻叠层；每回合10%双倍伤害）</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">

--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -769,12 +769,12 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>脚本32000(610, 550, 1000)；目标1；倍率[1000]；CD1</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>超级护主（独立）(610, 550, 1000)；目标1；倍率[1000]；CD1</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（主人受伤61%承担55%）</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤99(每层10.0%，999回合)</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>牛威（独立）；目标1；倍率[1000]；CD0；buff:叠层增伤99(每层10.0%，999回合)</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（每回合+10%魔攻叠层；70%随机减速/降攻；每回合首次伤害免疫；控制免疫未做）</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>被动触发；目标1；倍率[1000]；CD1；buff:叠层增伤3(每层15.0%，999回合)</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
+          <t>野蛮增长（独立）；目标1；倍率[1000]；CD0；buff:叠层增伤3(每层15.0%，999回合)</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>独立脚本（每回合+15%物攻3层；30%降攻20%；暴击叠层未做）</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">

--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -42,7 +42,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,11 +57,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,12 +86,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -105,9 +99,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -475,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -530,7 +521,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7">
@@ -543,67 +534,57 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>近似</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>说明</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>独立脚本：700001-700033 专用脚本</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>独立脚本：700001-700033 专用脚本</t>
+          <t>精确：属性/公式按说明落表</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>精确：属性/公式按说明落表</t>
+          <t>近似：属性/目标/消耗准确，伤害倍率或 buff 参数推断</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>近似：属性/目标/消耗准确，伤害倍率或 buff 参数推断</t>
+          <t>部分：部分机制已做，剩余机制未做</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>部分：部分机制已做，剩余机制未做</t>
+          <t>未实现：目前没有生效记录</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>未实现：目前没有生效记录</t>
+          <t>独立脚本均已编译、差分校验并热加载，战斗内触发仍建议实战确认</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
-        <is>
-          <t>独立脚本均已编译、差分校验并热加载，战斗内触发仍建议实战确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
         <is>
           <t>伤害倍率无法从客户端取得，均为推断值</t>
         </is>
@@ -632,3602 +613,3602 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>当前效果</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>技能说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="6" t="n">
         <v>60279</v>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>超级慈悲</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>召唤回主人血；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>独立脚本（召唤回主人28%生命）</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>战斗中闪现或被召唤时，将回复主人最大生命28%的生命值，最大回复不超过目标等级*40（宠物等级低于角色等级时，回复效率将会出现衰减）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="6" t="n">
         <v>60280</v>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>超级雷霆</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>召唤减主人冷却；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>独立脚本（召唤时主人技能冷却-3）</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>拥有用该技能的宠物，战斗中闪现或被召唤时，主人所有技能冷却回合-3</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="6" t="n">
         <v>60281</v>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>超级清心</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>召唤清心+控制免疫；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>独立脚本（召唤清心+控制免疫）</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>拥有用该技能的宠物，战斗中闪现或被召唤时，解除主人受到的控制状态，并附加控制免疫1~3回合</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>60282</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>超级护主</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>超级护主（独立）(610, 550, 1000)；目标1；倍率[1000]；CD1</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>独立脚本（主人受伤61%承担55%）</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>当主人受到伤害时，有61%几率为主人承担55%伤害</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>60283</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>超级涅槃</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>超级涅槃（独立）(400, 350, 0, 75)；目标1；倍率[1000]；CD4</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>独立脚本（主人死亡40%复活35%生命，上限等级×75）</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>主人死亡后有40%的几率将其复活，并恢复35%的生命,最大回复不超过主人等级*75</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>60284</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>超级破魔</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>攻击扣蓝+蓝耗25%；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>独立脚本（攻击扣蓝10%；蓝耗+25%已生效）</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>拥有该技能的宠物蓝耗增加25%，每次攻击将使目标减少最大值10%的魔法值，同个单位一回合内受到多次破魔时效果会降低</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>60285</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>超级神佑</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>超级神佑（独立）(140, 180, 220, 280, 1000, 0)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>独立脚本（死亡28%复活100%生命，体质修正）</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>死亡后有28%概率复活并恢复100%生命，与鬼魂、高级鬼魂共存时高级神佑技能无效，体质加点越低触发几率越高</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>60286</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>超级逃生</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>超级逃生（独立）(490, 0, 150)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>独立脚本（致命伤害49%回复150）</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>受到致命伤害时有49%几率回复150点生命</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>60288</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>超级反弹</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>超级反弹（独立）(350, 650)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>独立脚本（35%反弹65%）</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>受到攻击时有35%的几率反弹65%的伤害给目标</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="6" t="n">
         <v>60290</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>超级魔法还击</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>超级魔法还击（独立）(580, [60011, 60012, 60013)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>独立脚本（58%魔法还击）</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>受击近战攻击时有58%概率以魔法还击对方</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="6" t="n">
         <v>60291</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>超级报复</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>超级报复（独立）(500, 300, 100)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>独立脚本（低血增伤，阈值沿用10/30/50%）</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>生命值低于58%时，当生命值越低时所造成的伤害越高</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="6" t="n">
         <v>60301</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>超级审判</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>超级审判（独立）(350)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>独立脚本（对神佑/逃生目标+35%，击杀禁神佑）</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>对拥有神佑、逃生的敌人伤害结果增加35%，同时击杀敌人时，敌人无法触发神佑效果（可触发逃生）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="6" t="n">
         <v>60302</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>超级驱鬼</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>超级驱鬼（独立）(1000, 80)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>独立脚本（鬼魂2倍伤害，无视8%物防）</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>对带有鬼魂的怪物造成2倍伤害，并无视目标8%物理防御，若击杀可将其打出战斗场景外</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="6" t="n">
         <v>60304</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>超级物攻祝福</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>超级物攻祝福（独立）(380)；目标1；倍率[1000]；buff:物攻祝福(2回合)</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>独立脚本（回合初38%概率+10%物攻2回合）</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>回合初有38%概率为主人提升10%物攻，不占用出手回合，持续2回合</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="6" t="n">
         <v>60308</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>超级强体</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>生命=等级×55.0+380</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>永久提升宠物等级×55+380的生命值</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="6" t="n">
         <v>60311</v>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>超级逆击</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>超级逆击（独立）(330)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>独立脚本（对祝福目标+33%）</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>对身上有祝福类状态的目标额外造成33%的伤害</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="6" t="n">
         <v>60312</v>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>超级敏捷</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>攻速%+15.0%</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>永久提升15%攻速</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="6" t="n">
         <v>60313</v>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>超级防御</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>物防=等级×12.0+88</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>永久提升等级×12+88物防</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="6" t="n">
         <v>60314</v>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>超级魔法防御</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>魔防=等级×12.0+88</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>永久提升等级×12+88魔防</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="6" t="n">
         <v>60326</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>超级强击</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>命中+140；超级强击（独立）(150, 1700, 650)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>独立脚本（对宠物+15%，目标生命&gt;1.7倍再+65%）</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>对宠物单位伤害增加15%，若目标最大生命值超过己方1.7倍，额外造成65%的伤害</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="6" t="n">
         <v>60444</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>兵字秘</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>兵字秘（独立）(400)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>独立脚本（物穿40%）</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>九秘</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="6" t="n">
         <v>60447</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>斗字秘</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>生命%+5.0%，魔攻%+3.0%；斗字秘（独立）；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>独立脚本（40%追加130%魔法攻击）</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>九秘</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="6" t="n">
         <v>60448</v>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>行字秘</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>闪避+100，攻速%+35.0%</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>九秘</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="6" t="n">
         <v>60449</v>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>灵魂冲击</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>攻速%+20.0%；灵魂冲击（独立）(700, 700, 700, 700)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>独立脚本（70%眩晕1回合）</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>灵魂冲击</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="6" t="n">
         <v>60450</v>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>组字秘</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>生命+30000，伤害加成+15.0%；攻击触发伤害分担；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>独立脚本（攻击30%触发40%伤害分担2回合；属性已生效）</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>九秘</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="6" t="n">
         <v>60590</v>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>灵魂超度</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>魔攻%+20.0%；灵魂超度（条件倍率）()；目标4；倍率[1800]</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>独立脚本（&lt;50%生命2倍，否则150%；+20%魔攻）</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>对生命值低于50%的目标造成2倍魔法伤害，若目标生命值超过50%，则造成150%的魔法伤害，永久提升20%魔攻</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="6" t="n">
         <v>60603</v>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>枭刃</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>枭刃（1-2段）()；目标1；倍率[700, 700]</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>独立脚本（1–2段随机；倍率推断）</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>枭刃</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="6" t="n">
         <v>61064</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>法术吸血</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>法术吸血（独立）(1000, 150)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>独立脚本（法术吸血15%）</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>法术吸血</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="6" t="n">
         <v>67038</v>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>魔气入体</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>魔气入体（独立）(1000, 1000)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>独立脚本（必定魔气入体3回合）</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>魔气入体</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="6" t="n">
         <v>67067</v>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>魔域</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>暴伤+40.0%</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>魔域</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="6" t="n">
         <v>67068</v>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>修罗觉醒</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>暴击+25.0%，物伤加成+20.0%，攻速%+10.0%，魔防%+20.0%；回合末清异常()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>独立脚本（回合末50%清除自身异常）</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>修罗觉醒</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="6" t="n">
         <v>67074</v>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>推气过穴</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>推气过穴（独立治疗）(80, 200)；目标3；倍率[1000]；buff:持续回血(每回合5.0%，3回合)</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>独立脚本（3人，立即8%+200，每回合5%回血3回合）</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>推气过穴</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="6" t="n">
         <v>67075</v>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>郎神共舞</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>郎神共舞（独立）()；目标3；倍率[1600]；MP99</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>独立脚本（3目标魔法；50%主目标封心；70%一次免伤）</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>郎神共舞</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="6" t="n">
         <v>67076</v>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>神猿庇佑</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>生命%+30.0%，攻速%+15.0%，物防%+25.0%，魔防%+25.0%</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>神猿庇佑</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="6" t="n">
         <v>67077</v>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>战神护佑</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>攻速%+12.0%，魔攻%+10.0%，物防%+12.0%；击杀回血()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>独立脚本（击杀回复10%最大生命）</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>战神护佑</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="6" t="n">
         <v>67080</v>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>炸蓝</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>攻击扣蓝；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>独立脚本（攻击扣蓝15%）</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>炸蓝</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="6" t="n">
         <v>67081</v>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>神威</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>暴伤+20.0%；神威（独立）；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>独立脚本（80%魔法连击；神威状态/暴伤未做）</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>神威</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="6" t="n">
         <v>67082</v>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>牛威</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>牛威（独立）；目标1；倍率[1000]；CD0；buff:叠层增伤99(每层10.0%，999回合)</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>独立脚本（每回合+10%魔攻叠层；70%随机减速/降攻；每回合首次伤害免疫；控制免疫未做）</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>牛威</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="6" t="n">
         <v>67083</v>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>神牛意志</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>暴击+15.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%；攻击清增益；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>独立脚本（每次出手清除目标1个增益）</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>神牛意志</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="6" t="n">
         <v>67085</v>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>天诛</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>天诛（独立）()；目标4；倍率[1800]</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>独立脚本（4目标物理；暴击吸血20%）</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>天诛</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="n">
+      <c r="A42" s="6" t="n">
         <v>67086</v>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>神兵护佑</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>攻速%+12.0%，物防%+12.0%，魔防%+15.0%</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>神兵护佑</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="6" t="n">
         <v>67087</v>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>神兵加持</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>神兵加持（独立重放）()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>独立脚本（50%重放天诛）</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>神兵加持</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="6" t="n">
         <v>67091</v>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>白灵祝福</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>生命%+35.0%，攻速%+18.0%，物防%+30.0%，魔防%+30.0%；白灵祝福（独立护盾）；目标1；倍率[1000]；CD99</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>独立脚本（出场200%盾2回合；属性已生效）</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>白灵祝福</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="6" t="n">
         <v>67093</v>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>神猿加持</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>神猿加持（独立护盾）；目标1；倍率[1000]；CD99</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>独立脚本（出场200%盾2回合+20%反伤2回合）</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>神猿加持</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="n">
+      <c r="A46" s="6" t="n">
         <v>67097</v>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>神枭觉醒</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>暴击+20.0%，攻速%+15.0%，物攻%+15.0%，魔防%+20.0%；首次受击增伤()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>独立脚本（首次受击未死+20%物伤，本回合）</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>神枭觉醒</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="n">
+      <c r="A47" s="6" t="n">
         <v>67110</v>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>君皇横斩</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>真实伤害(500)；目标4；倍率[1800]</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>独立脚本（真实伤害）</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>君皇横斩</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="n">
+      <c r="A48" s="6" t="n">
         <v>67111</v>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>暗域</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>物伤加成+10.0%，物攻%+20.0%；同宠增伤；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>独立脚本（同阵营暗夜君王每只+5%横斩伤害，上限20%；另+10%物伤+20%物攻）</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <t>暗域</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="n">
+      <c r="A49" s="6" t="n">
         <v>67112</v>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>君王体魄</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>攻速%+12.0%，物攻%+15.0%，物防%+12.0%</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>君王体魄：</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="n">
+      <c r="A50" s="6" t="n">
         <v>67113</v>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>生命化泉</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>生命化泉（独立治疗）(120, 200)；目标4；倍率[1000]；buff:持续回血(每回合8.0%，3回合)</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>独立脚本（4人，立即12%+200，每回合8%回血3回合）</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>生命化泉</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="n">
+      <c r="A51" s="6" t="n">
         <v>67114</v>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>炼气化神</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>炼气化神（独立回蓝）(300, 0)；目标5；倍率[1000]；MP3；CD3</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>独立脚本（5人，回复30%最大魔法，CD3）</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>炼气化神</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="n">
+      <c r="A52" s="6" t="n">
         <v>67115</v>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>换天之术</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>换天之术（独立）；目标1；倍率[1000]；CD99</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>独立脚本（出场200%盾2回合+20%反伤；首次死亡复活20%）</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <t>换天之术</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="n">
+      <c r="A53" s="6" t="n">
         <v>67116</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>冥王庇佑</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>生命%+30.0%，攻速%+20.0%，物防%+25.0%，魔防%+25.0%；物理受击护盾(200, 300, 2)；目标1；倍率[1000]；CD1</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>独立脚本（物理受击护盾）</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>神猿庇佑</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="n">
+      <c r="A54" s="6" t="n">
         <v>67117</v>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>罗汉金钟</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>罗汉金钟（独立魔法盾）()；目标13；倍率[1000]；MP4；CD2</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>独立脚本（全体，魔法减伤50%3回合，CD2）</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>罗汉金钟</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="n">
+      <c r="A55" s="6" t="n">
         <v>67118</v>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>菩提明镜</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>菩提明镜（独立反伤盾）()；目标1；倍率[1000]；buff:反伤(35.0%反伤，3回合)</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>独立脚本（1人，反伤35%3回合）</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>菩提明镜</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="n">
+      <c r="A56" s="6" t="n">
         <v>67119</v>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>燃烧之光</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>辅助</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>燃烧之光（独立）()；目标13；倍率[1000]；MP4；CD2；buff:增伤(20.0%增伤，3回合)</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>独立脚本（全队+20%伤害3回合，CD2）</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t>燃烧之光</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="n">
+      <c r="A57" s="6" t="n">
         <v>67127</v>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>剑尊庇佑</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>生命%+30.0%，攻速%+20.0%，物防%+25.0%，魔防%+25.0%；出场盾+受击魔法盾；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>独立脚本（出场盾+受击魔法盾）</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>剑尊庇佑</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="n">
+      <c r="A58" s="6" t="n">
         <v>67130</v>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>兔击长空</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>兔击长空()；目标7；倍率[1200]；MP1；CD1</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>独立脚本（7目标物理；降速有几率暂按70%记录）</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t>兔击长空</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="n">
+      <c r="A59" s="6" t="n">
         <v>67131</v>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>正义审判</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>脚本20023(1, 250, 0)；目标1；倍率[0]</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>精确（当前生命25%脚本）</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>正义审判</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="n">
+      <c r="A60" s="6" t="n">
         <v>67132</v>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>野蛮增长</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>野蛮增长（独立）；目标1；倍率[1000]；CD0；buff:叠层增伤3(每层15.0%，999回合)</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>独立脚本（每回合+15%物攻3层；30%降攻20%；暴击叠层未做）</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <t>野蛮增长</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="n">
+      <c r="A61" s="6" t="n">
         <v>67133</v>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>神兔庇佑</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>攻速%+15.0%，物攻%+15.0%，物防%+20.0%，魔防%+20.0%；首次受击增伤+免伤盾()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>独立脚本（首次受击+20%物伤；受击30%几率30%减伤3回合）</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <t>神兔觉醒</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="n">
+      <c r="A62" s="6" t="n">
         <v>67200</v>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>阴阳怒焱</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>随机阳/阴形态()；目标1；倍率[1800]</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>独立脚本（40%阳焱全体+灼烧5%；60%阴焱2目标×2+50%眩晕）</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <t>阴阳怒焱</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="n">
+      <c r="A63" s="6" t="n">
         <v>67207</v>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>麒麟庇护</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>暴击+20.0%，攻速%+15.0%，魔攻%+15.0%，物防%+30.0%；攻击清增益；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>独立脚本（30%几率清除目标1个增益）</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>麒麟庇护</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="n">
+      <c r="A64" s="6" t="n">
         <v>67300</v>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>麒麟浴火</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>叠层+伤害分担；目标1；倍率[1000]；CD1；buff:叠层增伤3(每层10.0%，999回合)</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>独立脚本（叠层增伤+55%几率35%伤害分担）</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <t>麒麟浴火</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="n">
+      <c r="A65" s="6" t="n">
         <v>67302</v>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>麒麟御风</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>麒麟御风（独立护盾）；目标1；倍率[1000]；CD99</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>独立脚本（出场200%盾2回合；低血狂暴未做）</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>麒麟御风</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="n">
+      <c r="A66" s="6" t="n">
         <v>67304</v>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>花仙守护</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>花仙守护（独立）；目标1；倍率[1000]；CD99；buff:魔防(3回合)</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>独立脚本（首次死亡100%复活100%生命，+30%魔防3回合）</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <t>花仙守护</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="n">
+      <c r="A67" s="6" t="n">
         <v>67305</v>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>百花盾</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>减伤/反伤/沉默；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>独立脚本（减伤/反伤/沉默）</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <t>百花盾</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="n">
+      <c r="A68" s="6" t="n">
         <v>67306</v>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>仙泽福佑</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t>死亡回全队血；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>独立脚本（死亡回全队40%生命）</t>
         </is>
       </c>
-      <c r="F68" s="7" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <t>仙泽福佑</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="n">
+      <c r="A69" s="6" t="n">
         <v>67307</v>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>仙道神体</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>闪避+200，生命%+30.0%，物防%+25.0%，魔防%+25.0%；仙道神体（独立减伤盾）；目标1；倍率[1000]；CD4</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>独立脚本（初始70%减伤盾2回合，CD5）</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <t>仙道神体</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="n">
+      <c r="A70" s="6" t="n">
         <v>67308</v>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>身外化身</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:复活(80.0%生命复活，999回合)</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>身外化身（蛋形）；目标1；倍率[1000]；CD2</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>独立脚本（致命伤害变蛋保留80%生命；蛋破则死；回合末涅槃；CD3）</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <t>身外化身</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="n">
+      <c r="A71" s="6" t="n">
         <v>67309</v>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>金箍棒头</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>金箍棒头()；目标3×3；倍率[466, 466, 468]；3段</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>独立脚本（3×3物理；金刚/怒目有几率暂按70%记录）</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <t>金箍棒头</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="n">
+      <c r="A72" s="6" t="n">
         <v>67310</v>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>筋斗云决</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
         <is>
           <t>速度条件增伤/减伤；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>独立脚本（速度条件增伤/减伤）</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <t>筋斗云决</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="7" t="n">
+      <c r="A73" s="6" t="n">
         <v>67311</v>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>法天象地</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>暴击+10.0%，攻速%+15.0%，物攻%+15.0%，魔防%+25.0%</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>法天象地</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="n">
+      <c r="A74" s="6" t="n">
         <v>67314</v>
       </c>
-      <c r="B74" s="7" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>神隐</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>神隐（独立）；目标1；倍率[1000]；CD0</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>独立脚本（出场/召唤隐身2回合可攻击）</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <t>神隐</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="7" t="n">
+      <c r="A75" s="6" t="n">
         <v>67315</v>
       </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>金刚之躯</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>魔法暴击+10.0%，攻速%+10.0%，魔攻%+15.0%，物防%+30.0%；金刚之躯（独立）；目标1；倍率[1000]；CD0</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>独立脚本（受击70%概率20%减伤2回合）</t>
         </is>
       </c>
-      <c r="F75" s="7" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>金刚之躯</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="7" t="n">
+      <c r="A76" s="6" t="n">
         <v>67316</v>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>三味真火</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>三味真火()；目标3×3；倍率[466, 466, 468]；3段</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
+      <c r="E76" s="7" t="inlineStr">
         <is>
           <t>独立脚本（3×3魔法；天残/迟暮有几率暂按70%记录）</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <t>三味真火</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="7" t="n">
+      <c r="A77" s="6" t="n">
         <v>67330</v>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>八方俱灭</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>八方俱灭（独立）()；目标4×2；倍率[700, 700]；2段</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>独立脚本（2×4物理；主目标暴击吸血50%）</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <t>八方俱灭</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="n">
+      <c r="A78" s="6" t="n">
         <v>67331</v>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>死亡冲锋</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>周期攻速/物攻()；目标1；倍率[1000]；CD1；buff:攻速(攻速+20.0%，2回合)、物攻(物攻+30.0%，2回合)</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="E78" s="7" t="inlineStr">
         <is>
           <t>独立脚本（每2回合攻速+20%/物攻+30%，持续2回合）</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <t>死亡冲锋</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="7" t="n">
+      <c r="A79" s="6" t="n">
         <v>67332</v>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>八方物连</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>八方物连（独立）(600, 0, 1350, 1350)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>独立脚本（60%物理连击，倍率沿用135%）</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <t>八方物连</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="7" t="n">
+      <c r="A80" s="6" t="n">
         <v>67333</v>
       </c>
-      <c r="B80" s="7" t="inlineStr">
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>战神圣体</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
         <is>
           <t>暴击+10.0%，攻速%+15.0%，物攻%+18.0%，魔防%+25.0%；攻击为主人加怒；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t>独立脚本（60%攻击为主人+5怒气；属性已生效）</t>
         </is>
       </c>
-      <c r="F80" s="7" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <t>战神圣体</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="7" t="n">
+      <c r="A81" s="6" t="n">
         <v>67334</v>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>神龙吐珠</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>神龙吐珠（独立）()；目标4×2；倍率[700, 700]；2段；buff:法术吸血(10.0%吸血，1回合)</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>独立脚本（2×4魔法；10%法术吸血）</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>八方俱灭</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="7" t="n">
+      <c r="A82" s="6" t="n">
         <v>67335</v>
       </c>
-      <c r="B82" s="7" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>死亡追击</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
         <is>
           <t>击杀法术追击()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
+      <c r="E82" s="7" t="inlineStr">
         <is>
           <t>独立脚本（法术技能击杀后追击一次技能）</t>
         </is>
       </c>
-      <c r="F82" s="7" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <t>死亡追击</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="7" t="n">
+      <c r="A83" s="6" t="n">
         <v>67336</v>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>龙盾</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>龙盾（独立护盾）；目标1；倍率[1000]；CD99</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>独立脚本（出场100%盾1回合；低血狂暴未做）</t>
         </is>
       </c>
-      <c r="F83" s="7" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <t>龙盾</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="7" t="n">
+      <c r="A84" s="6" t="n">
         <v>67337</v>
       </c>
-      <c r="B84" s="7" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>龙尊道体</t>
         </is>
       </c>
-      <c r="C84" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
         <is>
           <t>魔法暴击+15.0%，攻速%+12.0%，魔攻%+15.0%，物防%+25.0%；龙尊道体（独立）；目标1；倍率[1000]；CD1</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t>独立脚本（致命伤害50%免疫每回合一次；带60352/60353时80%）</t>
         </is>
       </c>
-      <c r="F84" s="7" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <t>龙尊道体</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="7" t="n">
+      <c r="A85" s="6" t="n">
         <v>67338</v>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>玄女功</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>玄女功()；目标3/4/5；倍率[466, 466, 468]；3段</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>独立脚本（3/4/5目标物理）</t>
         </is>
       </c>
-      <c r="F85" s="7" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>玄女功</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="7" t="n">
+      <c r="A86" s="6" t="n">
         <v>67339</v>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>天地双连</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
         <is>
           <t>天地双连（独立）(700, 0, 1200, 1200)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E86" s="8" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>独立脚本（70%物理连击120%）</t>
         </is>
       </c>
-      <c r="F86" s="7" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <t>天地双连</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="7" t="n">
+      <c r="A87" s="6" t="n">
         <v>67340</v>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>玄天暴</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>随机双倍/三倍+速度增伤；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>独立脚本（随机双/三倍+速度增伤）</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <t>玄天暴</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="7" t="n">
+      <c r="A88" s="6" t="n">
         <v>67341</v>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>玄天盾</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D88" s="6" t="inlineStr">
         <is>
           <t>玄天盾（独立）；目标1；倍率[1000]；CD0</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>独立脚本（出场/召唤100%盾1回合；10%致命免疫）</t>
         </is>
       </c>
-      <c r="F88" s="7" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <t>玄天盾</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="7" t="n">
+      <c r="A89" s="6" t="n">
         <v>67342</v>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>玄女圣体</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>暴击+15.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%；攻击不加怒/扣目标怒；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>独立脚本（攻击不涨怒并扣第一目标5怒；属性已生效）</t>
         </is>
       </c>
-      <c r="F89" s="7" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>玄女圣体</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="7" t="n">
+      <c r="A90" s="6" t="n">
         <v>67343</v>
       </c>
-      <c r="B90" s="7" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>初音飓风</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr">
+      <c r="D90" s="6" t="inlineStr">
         <is>
           <t>初音飓风+驱散()；目标3/3/6；倍率[466, 466, 468]；3段</t>
         </is>
       </c>
-      <c r="E90" s="8" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>独立脚本（3/3/6魔法+必定驱散）</t>
         </is>
       </c>
-      <c r="F90" s="7" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <t>初音风暴</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="7" t="n">
+      <c r="A91" s="6" t="n">
         <v>67344</v>
       </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>乘风</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>乘风（独立）；目标1；倍率[1000]；CD0；buff:叠层增伤99(每层10.0%，999回合)</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>独立脚本（每回合+10%魔攻叠层）</t>
         </is>
       </c>
-      <c r="F91" s="7" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>乘风</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="7" t="n">
+      <c r="A92" s="6" t="n">
         <v>67345</v>
       </c>
-      <c r="B92" s="7" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>天佑</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
         <is>
           <t>复活+伤害分担；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E92" s="8" t="inlineStr">
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t>独立脚本（首次死亡50%复活；每回合40%几率35%伤害分担2回合）</t>
         </is>
       </c>
-      <c r="F92" s="7" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <t>天佑</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="7" t="n">
+      <c r="A93" s="6" t="n">
         <v>67346</v>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>风盾</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>风盾（独立护盾）；目标1；倍率[1000]；CD99</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>独立脚本（前2回合+20%伤害/攻速；出场200%盾1回合）</t>
         </is>
       </c>
-      <c r="F93" s="7" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>风盾</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="7" t="n">
+      <c r="A94" s="6" t="n">
         <v>67347</v>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>初音圣体</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
         <is>
           <t>魔法暴击+20.0%，攻速%+18.0%，魔攻%+15.0%，物防%+25.0%；初音圣体（阈值减伤）()；目标1；倍率[1000]；CD2</t>
         </is>
       </c>
-      <c r="E94" s="8" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>独立脚本（单次伤害&gt;50%生命时80%几率降至40%，+20%伤害2回合，CD3；覆盖普通/反击/协助伤害）</t>
         </is>
       </c>
-      <c r="F94" s="7" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <t>初音圣体</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="7" t="n">
+      <c r="A95" s="6" t="n">
         <v>67348</v>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>穷凶烈爪</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>穷凶烈爪+暴击吸血()；目标2/3；倍率[700, 700]；2段</t>
         </is>
       </c>
-      <c r="E95" s="8" t="inlineStr">
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>独立脚本（2/3目标物理；主目标暴击吸血30%；护盾有几率暂按70%记录）</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>穷凶烈爪</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="7" t="n">
+      <c r="A96" s="6" t="n">
         <v>67349</v>
       </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>列字秘</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
         <is>
           <t>物攻%+5.0%，魔攻%+3.0%；列字秘（独立追击）()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E96" s="8" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>独立脚本（技能击杀追击最多2次；+5%物攻/+3%魔攻）</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <t>九秘</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="7" t="n">
+      <c r="A97" s="6" t="n">
         <v>67352</v>
       </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>穷奇圣体</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
         <is>
           <t>暴击+5.0%，攻速%+10.0%，物攻%+10.0%；穷奇圣体（独立）()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E97" s="8" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>独立脚本（攻击人物无视10%物魔防）</t>
         </is>
       </c>
-      <c r="F97" s="7" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <t>穷奇圣体</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="7" t="n">
+      <c r="A98" s="6" t="n">
         <v>67353</v>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>封阳击</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr">
+      <c r="D98" s="6" t="inlineStr">
         <is>
           <t>封阳击（独立物理）()；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
         </is>
       </c>
-      <c r="E98" s="8" t="inlineStr">
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>独立脚本（5–8段随机；击杀后自动转火；物理攻击脚本已修正）</t>
         </is>
       </c>
-      <c r="F98" s="7" t="inlineStr">
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <t>封阳击</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="7" t="n">
+      <c r="A99" s="6" t="n">
         <v>67354</v>
       </c>
-      <c r="B99" s="7" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>突袭</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>突袭（独立）(280)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E99" s="8" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>独立脚本（物穿28%）</t>
         </is>
       </c>
-      <c r="F99" s="7" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <t>突袭</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="7" t="n">
+      <c r="A100" s="6" t="n">
         <v>67355</v>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>禁魂</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
         <is>
           <t>禁魂（独立）(200, 200)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E100" s="8" t="inlineStr">
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t>独立脚本（20%禁魂5回合）</t>
         </is>
       </c>
-      <c r="F100" s="7" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <t>禁魂</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="7" t="n">
+      <c r="A101" s="6" t="n">
         <v>67356</v>
       </c>
-      <c r="B101" s="7" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>封盾</t>
         </is>
       </c>
-      <c r="C101" s="7" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D101" s="7" t="inlineStr">
+      <c r="D101" s="6" t="inlineStr">
         <is>
           <t>封盾（独立护盾）；目标1；倍率[1000]；CD99</t>
         </is>
       </c>
-      <c r="E101" s="8" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>独立脚本（前3回合+30%伤害/40%攻速；出场200%盾1回合）</t>
         </is>
       </c>
-      <c r="F101" s="7" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <t>封盾</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="7" t="n">
+      <c r="A102" s="6" t="n">
         <v>67357</v>
       </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>封阳圣体</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
         <is>
           <t>暴击+20.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%；封阳圣体（独立）()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E102" s="8" t="inlineStr">
+      <c r="E102" s="7" t="inlineStr">
         <is>
           <t>独立脚本（攻击人物无视35%物魔防）</t>
         </is>
       </c>
-      <c r="F102" s="7" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <t>封阳圣体</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="7" t="n">
+      <c r="A103" s="6" t="n">
         <v>67358</v>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>太初决</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="D103" s="6" t="inlineStr">
         <is>
           <t>太初决+驱散()；目标3/4/10；倍率[466, 466, 468]；3段；buff:小萌羊(3回合)、小萌羊(3回合)、小萌羊(3回合)</t>
         </is>
       </c>
-      <c r="E103" s="8" t="inlineStr">
+      <c r="E103" s="7" t="inlineStr">
         <is>
           <t>独立脚本（3/4/10魔法+必定驱散；20%小萌羊3回合）</t>
         </is>
       </c>
-      <c r="F103" s="7" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <t>太初决</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="7" t="n">
+      <c r="A104" s="6" t="n">
         <v>67359</v>
       </c>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>破竹</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
         <is>
           <t>法术吸血+受击减伤；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E104" s="8" t="inlineStr">
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>独立脚本（25%法术吸血+受击减伤）</t>
         </is>
       </c>
-      <c r="F104" s="7" t="inlineStr">
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <t>破竹</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="7" t="n">
+      <c r="A105" s="6" t="n">
         <v>67360</v>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>扶摇</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
         <is>
           <t>扶摇（独立）；目标1；倍率[1000]；CD0；buff:叠层增伤99(每层15.0%，999回合)</t>
         </is>
       </c>
-      <c r="E105" s="8" t="inlineStr">
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>独立脚本（每回合+15%魔攻叠层；每回合10%双倍伤害）</t>
         </is>
       </c>
-      <c r="F105" s="7" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <t>扶摇</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="7" t="n">
+      <c r="A106" s="6" t="n">
         <v>67361</v>
       </c>
-      <c r="B106" s="7" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>搬山</t>
         </is>
       </c>
-      <c r="C106" s="7" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D106" s="7" t="inlineStr">
+      <c r="D106" s="6" t="inlineStr">
         <is>
           <t>搬山护盾/增伤/复活()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E106" s="8" t="inlineStr">
+      <c r="E106" s="7" t="inlineStr">
         <is>
           <t>独立脚本（前3回合魔伤+40%/攻速+30%；出场200%护盾1回合；首次死亡60%复活）</t>
         </is>
       </c>
-      <c r="F106" s="7" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <t>搬山</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="7" t="n">
+      <c r="A107" s="6" t="n">
         <v>67362</v>
       </c>
-      <c r="B107" s="7" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>太初圣体</t>
         </is>
       </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；太初圣体（独立）()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E107" s="8" t="inlineStr">
+      <c r="E107" s="7" t="inlineStr">
         <is>
           <t>独立脚本（攻击人物无视30%物魔防）</t>
         </is>
       </c>
-      <c r="F107" s="7" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <t>太初圣体</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="7" t="n">
+      <c r="A108" s="6" t="n">
         <v>67363</v>
       </c>
-      <c r="B108" s="7" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>死亡镰刀</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="D108" s="6" t="inlineStr">
         <is>
           <t>魔法攻击(0)；目标1×5；倍率[260, 260, 260, 260, 260]；5段</t>
         </is>
       </c>
-      <c r="E108" s="8" t="inlineStr">
+      <c r="E108" s="7" t="inlineStr">
         <is>
           <t>独立脚本（5–8段随机；击杀后自动转火；每段20%眩晕2回合）</t>
         </is>
       </c>
-      <c r="F108" s="7" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <t>死亡镰刀</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="7" t="n">
+      <c r="A109" s="6" t="n">
         <v>67364</v>
       </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>破道</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D109" s="7" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
         <is>
           <t>破道（独立）(300)；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E109" s="8" t="inlineStr">
+      <c r="E109" s="7" t="inlineStr">
         <is>
           <t>独立脚本（法穿30%）</t>
         </is>
       </c>
-      <c r="F109" s="7" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <t>破道</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="7" t="n">
+      <c r="A110" s="6" t="n">
         <v>67365</v>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>转阳</t>
         </is>
       </c>
-      <c r="C110" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="inlineStr">
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
         <is>
           <t>击杀回血+燃火；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E110" s="8" t="inlineStr">
+      <c r="E110" s="7" t="inlineStr">
         <is>
           <t>独立脚本（击杀回血+燃火增伤）</t>
         </is>
       </c>
-      <c r="F110" s="7" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <t>转阳</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="7" t="n">
+      <c r="A111" s="6" t="n">
         <v>67366</v>
       </c>
-      <c r="B111" s="7" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>死神盾</t>
         </is>
       </c>
-      <c r="C111" s="7" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D111" s="7" t="inlineStr">
+      <c r="D111" s="6" t="inlineStr">
         <is>
           <t>死神盾（独立护盾）；目标1；倍率[1000]；CD99</t>
         </is>
       </c>
-      <c r="E111" s="8" t="inlineStr">
+      <c r="E111" s="7" t="inlineStr">
         <is>
           <t>独立脚本（前3回合+30%伤害/40%攻速；出场挡6次盾1回合）</t>
         </is>
       </c>
-      <c r="F111" s="7" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <t>死神盾</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="7" t="n">
+      <c r="A112" s="6" t="n">
         <v>67367</v>
       </c>
-      <c r="B112" s="7" t="inlineStr">
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>死神神体</t>
         </is>
       </c>
-      <c r="C112" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D112" s="7" t="inlineStr">
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
         <is>
           <t>魔法暴击+20.0%，攻速%+20.0%，魔攻%+20.0%，物防%+25.0%；无视防御+阵亡增伤()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E112" s="8" t="inlineStr">
+      <c r="E112" s="7" t="inlineStr">
         <is>
           <t>独立脚本（攻击人物无视30%防；每个阵亡友方+10%伤害/+20%魔防）</t>
         </is>
       </c>
-      <c r="F112" s="7" t="inlineStr">
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <t>死神神体</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="7" t="n">
+      <c r="A113" s="6" t="n">
         <v>67368</v>
       </c>
-      <c r="B113" s="7" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>无忧击</t>
         </is>
       </c>
-      <c r="C113" s="7" t="inlineStr">
+      <c r="C113" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D113" s="7" t="inlineStr">
+      <c r="D113" s="6" t="inlineStr">
         <is>
           <t>附加治疗/护盾()；目标4×3；倍率[466, 466, 468]；3段</t>
         </is>
       </c>
-      <c r="E113" s="8" t="inlineStr">
+      <c r="E113" s="7" t="inlineStr">
         <is>
           <t>独立脚本（每段附加治疗+20%护盾近似）</t>
         </is>
       </c>
-      <c r="F113" s="7" t="inlineStr">
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <t>无忧击</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="7" t="n">
+      <c r="A114" s="6" t="n">
         <v>67369</v>
       </c>
-      <c r="B114" s="7" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>化魂</t>
         </is>
       </c>
-      <c r="C114" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D114" s="7" t="inlineStr">
-        <is>
-          <t>被动触发；目标1；倍率[1000]；CD99；buff:复活(150.0%生命复活，999回合)</t>
-        </is>
-      </c>
-      <c r="E114" s="9" t="inlineStr">
-        <is>
-          <t>近似（触发脚本）</t>
-        </is>
-      </c>
-      <c r="F114" s="7" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>化魂（蛋形）；目标1；倍率[1000]；CD2</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>独立脚本（致命伤害变蛋保留150%生命；蛋破则死；回合末恢复80%；CD3）</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <t>化魂</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="7" t="n">
+      <c r="A115" s="6" t="n">
         <v>67370</v>
       </c>
-      <c r="B115" s="7" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>叠法</t>
         </is>
       </c>
-      <c r="C115" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D115" s="7" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>叠法（独立重放）()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E115" s="8" t="inlineStr">
+      <c r="E115" s="7" t="inlineStr">
         <is>
           <t>独立脚本（30%重放无忧击70%伤害）</t>
         </is>
       </c>
-      <c r="F115" s="7" t="inlineStr">
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <t>叠法</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="7" t="n">
+      <c r="A116" s="6" t="n">
         <v>67371</v>
       </c>
-      <c r="B116" s="7" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>亡川盾</t>
         </is>
       </c>
-      <c r="C116" s="7" t="inlineStr">
+      <c r="C116" s="6" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr">
+      <c r="D116" s="6" t="inlineStr">
         <is>
           <t>亡川盾（独立护盾）；目标1；倍率[1000]；CD99</t>
         </is>
       </c>
-      <c r="E116" s="8" t="inlineStr">
+      <c r="E116" s="7" t="inlineStr">
         <is>
           <t>独立脚本（前3回合+30%伤害/30%攻速；出场挡6次盾1回合）</t>
         </is>
       </c>
-      <c r="F116" s="7" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <t>亡川盾</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="7" t="n">
+      <c r="A117" s="6" t="n">
         <v>67372</v>
       </c>
-      <c r="B117" s="7" t="inlineStr">
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>亡川神体</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D117" s="7" t="inlineStr">
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t>暴击+20.0%，攻速%+15.0%，物攻%+20.0%，魔防%+25.0%；亡川神体（独立）()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E117" s="8" t="inlineStr">
+      <c r="E117" s="7" t="inlineStr">
         <is>
           <t>独立脚本（攻击人物无视35%物魔防）</t>
         </is>
       </c>
-      <c r="F117" s="7" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <t>亡川神体</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="7" t="n">
+      <c r="A118" s="6" t="n">
         <v>67378</v>
       </c>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="B118" s="6" t="inlineStr">
         <is>
           <t>乾坤天降</t>
         </is>
       </c>
-      <c r="C118" s="7" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>主动</t>
         </is>
       </c>
-      <c r="D118" s="7" t="inlineStr">
+      <c r="D118" s="6" t="inlineStr">
         <is>
           <t>乾坤天降（风雷）()；目标6；倍率[1200]</t>
         </is>
       </c>
-      <c r="E118" s="8" t="inlineStr">
+      <c r="E118" s="7" t="inlineStr">
         <is>
           <t>独立脚本（主目标+相邻5目标同倍率；释放后+15%物攻/速度/生命；风雷护盾70%几率250%生命2回合）</t>
         </is>
       </c>
-      <c r="F118" s="7" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <t>乾坤·天降</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="7" t="n">
+      <c r="A119" s="6" t="n">
         <v>67379</v>
       </c>
-      <c r="B119" s="7" t="inlineStr">
+      <c r="B119" s="6" t="inlineStr">
         <is>
           <t>九龙神火</t>
         </is>
       </c>
-      <c r="C119" s="7" t="inlineStr">
-        <is>
-          <t>触发</t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="inlineStr">
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>触发</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
         <is>
           <t>伤害加成+30.0%，攻速%+30.0%，魔防%+30.0%；九龙神火（独立重放）()；目标1；倍率[1000]</t>
         </is>
       </c>
-      <c r="E119" s="8" t="inlineStr">
+      <c r="E119" s="7" t="inlineStr">
         <is>
           <t>独立脚本（释放乾坤天降40%额外释放；+30%伤害/攻速/魔防）</t>
         </is>
       </c>
-      <c r="F119" s="7" t="inlineStr">
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <t>九龙神火</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="7" t="n">
+      <c r="A120" s="6" t="n">
         <v>67503</v>
       </c>
-      <c r="B120" s="7" t="inlineStr">
+      <c r="B120" s="6" t="inlineStr">
         <is>
           <t>者字秘</t>
         </is>
       </c>
-      <c r="C120" s="7" t="inlineStr">
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>被动</t>
         </is>
       </c>
-      <c r="D120" s="7" t="inlineStr">
+      <c r="D120" s="6" t="inlineStr">
         <is>
           <t>生命=等级×80.0+1000</t>
         </is>
       </c>
-      <c r="E120" s="8" t="inlineStr">
+      <c r="E120" s="7" t="inlineStr">
         <is>
           <t>精确（属性）</t>
         </is>
       </c>
-      <c r="F120" s="7" t="inlineStr">
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <t>九秘</t>
         </is>
@@ -4257,32 +4238,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>当前效果</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>技能说明</t>
         </is>

--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>攻速%+20.0%；灵魂冲击（独立）(700, 700, 700, 700)；目标1；倍率[1000]</t>
+          <t>攻速%+20.0%；灵魂冲击（独立）(900, 900, 900, 900)；目标1；倍率[1000]</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（70%眩晕1回合）</t>
+          <t>独立脚本（90%眩晕1回合）</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（攻击30%触发40%伤害分担2回合；属性已生效）</t>
+          <t>独立脚本（攻击70%触发40%伤害分担2回合；属性已生效）</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（3目标魔法；50%主目标封心；70%一次免伤）</t>
+          <t>独立脚本（3目标魔法；50%主目标封心；90%一次免伤）</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（80%魔法连击；神威状态/暴伤未做）</t>
+          <t>独立脚本（80%魔法连击；神威状态（一定概率70%）/暴伤未做）</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（7目标物理；降速有几率暂按70%记录）</t>
+          <t>独立脚本（7目标物理；降速有几率（50%）记录）</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（首次受击+20%物伤；受击30%几率30%减伤3回合）</t>
+          <t>独立脚本（首次受击+20%物伤；受击50%几率30%减伤3回合）</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（40%阳焱全体+灼烧5%；60%阴焱2目标×2+50%眩晕）</t>
+          <t>独立脚本（40%阳焱全体+灼烧5%（50%几率）；60%阴焱2目标×2+50%眩晕）</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（30%几率清除目标1个增益）</t>
+          <t>独立脚本（70%几率清除目标1个增益）</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（出场200%盾2回合；低血狂暴未做）</t>
+          <t>独立脚本（出场200%盾2回合；低血狂暴（有几率50%）未做）</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（3×3物理；金刚/怒目有几率暂按70%记录）</t>
+          <t>独立脚本（3×3物理；金刚/怒目有几率（50%）记录）</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（3×3魔法；天残/迟暮有几率暂按70%记录）</t>
+          <t>独立脚本（3×3魔法；天残/迟暮有几率（50%）记录）</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（出场100%盾1回合；低血狂暴未做）</t>
+          <t>独立脚本（出场100%盾1回合；低血狂暴（有几率50%）未做）</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（2/3目标物理；主目标暴击吸血30%；护盾有几率暂按70%记录）</t>
+          <t>独立脚本（2/3目标物理；主目标暴击吸血30%；护盾（极大几率90%）记录）</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（每段附加治疗+20%护盾近似）</t>
+          <t>独立脚本（每段附加治疗+20%护盾近似；孱弱（有几率50%）未做）</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（主目标+相邻5目标同倍率；释放后+15%物攻/速度/生命；风雷护盾70%几率250%生命2回合）</t>
+          <t>独立脚本（主目标+相邻5目标同倍率；释放后+15%物攻/速度/生命；风雷护盾50%几率250%生命2回合）</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">

--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -2345,7 +2345,7 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（7目标物理；降速有几率（50%）记录）</t>
+          <t>独立脚本（7目标物理；50%降速20%3回合）</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（3×3物理；金刚/怒目有几率（50%）记录）</t>
+          <t>独立脚本（3×3物理；50%金刚/怒目2回合；金刚物防无视未做）</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（3×3魔法；天残/迟暮有几率（50%）记录）</t>
+          <t>独立脚本（3×3魔法；50%天残/迟暮2回合）</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（2/3目标物理；主目标暴击吸血30%；护盾（极大几率90%）记录）</t>
+          <t>独立脚本（2/3目标物理；主目标暴击吸血30%；90%每回合挡1次盾）</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（每段附加治疗+20%护盾近似；孱弱（有几率50%）未做）</t>
+          <t>独立脚本（每段治疗/护盾；50%孱弱-30%伤害/攻速）</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">

--- a/docs/技能效果表.xlsx
+++ b/docs/技能效果表.xlsx
@@ -1745,7 +1745,7 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（80%魔法连击；神威状态（一定概率70%）/暴伤未做）</t>
+          <t>独立脚本（80%魔法连击；70%神威双倍法术伤害；暴伤+20%属性）</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（每回合+10%魔攻叠层；70%随机减速/降攻；每回合首次伤害免疫；控制免疫未做）</t>
+          <t>独立脚本（每回合+10%魔攻叠层；70%随机减速/降攻；每回合首次伤害或控制免疫）</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>独立脚本（每回合+15%物攻3层；30%降攻20%；暴击叠层未做）</t>
+          <t>独立脚本（每回合+15%物攻3层；每次出手+10%暴击直到暴击；30%降攻20%）</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
